--- a/Systemdaten/Globale_KontenRegeln.xlsx
+++ b/Systemdaten/Globale_KontenRegeln.xlsx
@@ -7178,7 +7178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1204"/>
+  <dimension ref="A1:G1230"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -13306,7 +13306,6 @@
           <t>HOLZNER METZGEREI - ANDREAS-HOFER-STRASSE 15 - 39011 LANA</t>
         </is>
       </c>
-      <c r="F1030" t="inlineStr"/>
       <c r="G1030" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -15337,7 +15336,6 @@
           <t>HOLZNER GMBH - ANDREAS HOFER STR. 15 - 39011 LANA BZ</t>
         </is>
       </c>
-      <c r="F1085" t="inlineStr"/>
       <c r="G1085" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -15777,7 +15775,6 @@
           <t>LIEFERUNGSNR. 05-25SV13288 VOM 02/12/25</t>
         </is>
       </c>
-      <c r="F1097" t="inlineStr"/>
       <c r="G1097" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -15810,7 +15807,6 @@
           <t>IHRE AUFTRAGSREF. 51002 VOM 01/12/25</t>
         </is>
       </c>
-      <c r="F1098" t="inlineStr"/>
       <c r="G1098" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -15991,7 +15987,6 @@
           <t>LIEFERUNGSNR. 05-25SV13332 VOM 03/12/25</t>
         </is>
       </c>
-      <c r="F1103" t="inlineStr"/>
       <c r="G1103" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16024,7 +16019,6 @@
           <t>IHRE AUFTRAGSREF. 51093 VOM 02/12/25</t>
         </is>
       </c>
-      <c r="F1104" t="inlineStr"/>
       <c r="G1104" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16057,7 +16051,6 @@
           <t>LIEFERUNGSNR. 05-25SV13377 VOM 04/12/25</t>
         </is>
       </c>
-      <c r="F1105" t="inlineStr"/>
       <c r="G1105" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16090,7 +16083,6 @@
           <t>IHRE AUFTRAGSREF. 51209 VOM 03/12/25</t>
         </is>
       </c>
-      <c r="F1106" t="inlineStr"/>
       <c r="G1106" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16197,7 +16189,6 @@
           <t>LIEFERUNGSNR. 05-25SV13421 VOM 05/12/25</t>
         </is>
       </c>
-      <c r="F1109" t="inlineStr"/>
       <c r="G1109" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16230,7 +16221,6 @@
           <t>IHRE AUFTRAGSREF. 51273 VOM 04/12/25</t>
         </is>
       </c>
-      <c r="F1110" t="inlineStr"/>
       <c r="G1110" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16263,7 +16253,6 @@
           <t>LIEFERUNGSNR. 05-25SV13473 VOM 06/12/25</t>
         </is>
       </c>
-      <c r="F1111" t="inlineStr"/>
       <c r="G1111" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16296,7 +16285,6 @@
           <t>IHRE AUFTRAGSREF. 51449 VOM 05/12/25</t>
         </is>
       </c>
-      <c r="F1112" t="inlineStr"/>
       <c r="G1112" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16329,7 +16317,6 @@
           <t>LIEFERUNGSNR. 05-25SV13561 VOM 10/12/25</t>
         </is>
       </c>
-      <c r="F1113" t="inlineStr"/>
       <c r="G1113" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16362,7 +16349,6 @@
           <t>IHRE AUFTRAGSREF. 51654 VOM 09/12/25</t>
         </is>
       </c>
-      <c r="F1114" t="inlineStr"/>
       <c r="G1114" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16395,7 +16381,6 @@
           <t>LIEFERUNGSNR. 05-25SV13653 VOM 12/12/25</t>
         </is>
       </c>
-      <c r="F1115" t="inlineStr"/>
       <c r="G1115" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16428,7 +16413,6 @@
           <t>IHRE AUFTRAGSREF. 51833 VOM 11/12/25</t>
         </is>
       </c>
-      <c r="F1116" t="inlineStr"/>
       <c r="G1116" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16498,7 +16482,6 @@
           <t>LIEFERUNGSNR. 05-25SV13691 VOM 13/12/25</t>
         </is>
       </c>
-      <c r="F1118" t="inlineStr"/>
       <c r="G1118" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -16531,7 +16514,6 @@
           <t>IHRE AUFTRAGSREF. 52016 VOM 12/12/25</t>
         </is>
       </c>
-      <c r="F1119" t="inlineStr"/>
       <c r="G1119" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
@@ -19678,6 +19660,968 @@
         </is>
       </c>
       <c r="G1204" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>02578060218</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Purnamh GmbH/SRL Società Benefit</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH HOLZNER ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>BERGAPFELSAFT NATUR 0</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>00137840203</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>LEVONI S.P.A. Societa Benefit</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>HOLZNER SRL_.</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>SALAME UNGHERESE 3</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>VENTRICINA 2</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 1 IN PERCENTUALE 24</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>GUANCIALE RUSTICO 1</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>PECORINO DI ROCCA 2</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>PARMA S/O 18M SPEC 7</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>SALAME ILGENTILE 1</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 6 IN PERCENTUALE 15</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>FINOCCHIONA IGP 2</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 8 IN PERCENTUALE 21</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>SAL. STOFELOTTO 2</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 10 IN PERCENTUALE 19</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>S. BOCC.FILZE 35G PC1</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 12 IN PERCENTUALE 15</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>CULAT.DIAM S/O SV4</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 16 IN PERCENTUALE 4</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 18 IN PERCENTUALE 16</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>00772580361</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Villani S.p.A.</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>HOLZNER GMBH - SRL</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>RIGA AGGIUNTIVA PER SCONTO CUMULATIVO RIGA 20 IN PERCENTUALE 15</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>01192160214</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Rinner Alexander &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Holzner GmbH  (Holzner GmbH)</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>BIO SALAMI PIKANT 1/2</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>01192160214</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Rinner Alexander &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Holzner GmbH  (Holzner GmbH)</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>SALAMI MIT REH 1/2</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>01192160214</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Rinner Alexander &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Holzner GmbH  (Holzner GmbH)</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>SALAMI MIT HIRSCH 1/2</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>01192160214</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Rinner Alexander &amp; CO KG</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Holzner GmbH  (Holzner GmbH)</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>KRÄUTERSALAMI 1/2</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>00101080216</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Milchhof Meran Gen. u. landw. Ges./Latteria Sociale Merano Soc. Agr. Cop.</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Holzner GmbH</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>FRISCHMILCH 0</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>00101080216</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Milchhof Meran Gen. u. landw. Ges./Latteria Sociale Merano Soc. Agr. Cop.</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Holzner GmbH</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>FRISCHRAHM 0</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>AUSSTEHEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>01695950210</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Günther Schmidhammer</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>02977480215</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Holzner GmbH</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>KARTON EIER ZU 180 STÜCK EIER CAT. A GRÖE M/L 0</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>100 / 801006</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
         <is>
           <t>AUSSTEHEND</t>
         </is>

--- a/Systemdaten/Globale_KontenRegeln.xlsx
+++ b/Systemdaten/Globale_KontenRegeln.xlsx
@@ -1,16 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontenplan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lieferanten-Regeln" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stichwort-Regeln" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KI-Zuweisungen" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lieferanten-Regeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stichwort-Regeln" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="KI-Zuweisungen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -484,6617 +482,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="14.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="31" bestFit="1" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Konto-Nummer</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Bezeichnung</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dropdown (Wird automatisch erstellt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Crediti verso Soci</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>110000 - Crediti verso Soci</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>121000</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Immobilizzazioni Immateriali</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>121000 - Immobilizzazioni Immateriali</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>122000</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Immobilizzazioni Materiali</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>122000 - Immobilizzazioni Materiali</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>123000</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Immobilizzazioni Finanziarie</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>123000 - Immobilizzazioni Finanziarie</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>131000</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rimanenze</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>131000 - Rimanenze</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>132100</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Crediti v/Clienti Italia</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>132100 - Crediti v/Clienti Italia</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>132200</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Crediti v/Clienti Estero</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>132200 - Crediti v/Clienti Estero</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>134001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cassa contanti</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>134001 - Cassa contanti</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>134010</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Banca c/c</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>134010 - Banca c/c</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>140000</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ratei e Risconti Attivi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>140000 - Ratei e Risconti Attivi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>211000</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capitale Sociale</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>211000 - Capitale Sociale</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>212000</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Riserve</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>212000 - Riserve</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>213000</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Utile/Perdita desercizio</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>213000 - Utile/Perdita desercizio</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Fondi per Rischi e Oneri</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>220000 - Fondi per Rischi e Oneri</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>230000</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TFR</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>230000 - TFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>241000</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Debiti v/Banche</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>241000 - Debiti v/Banche</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>242100</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Debiti v/Fornitori Italia</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>242100 - Debiti v/Fornitori Italia</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>242200</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Debiti v/Fornitori Estero</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>242200 - Debiti v/Fornitori Estero</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>243000</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Debiti Tributari</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>243000 - Debiti Tributari</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>244000</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Debiti v/Istituti previdenziali</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>244000 - Debiti v/Istituti previdenziali</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Ratei e Risconti Passivi</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>250000 - Ratei e Risconti Passivi</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>310000</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Acquisti di Materie e Merci</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>310000 - Acquisti di Materie e Merci</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>320010</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Spese di consulenza</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>320010 - Spese di consulenza</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>320020</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Utenze energia, gas, telefono</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>320020 - Utenze energia, gas, telefono</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Costi per Godimento Beni di Terzi</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>330000 - Costi per Godimento Beni di Terzi</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>341000</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Salari e Stipendi</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>341000 - Salari e Stipendi</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>342000</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Oneri Sociali</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>342000 - Oneri Sociali</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>343000</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Quota TFR</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>343000 - Quota TFR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>350000</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ammortamenti e Svalutazioni</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>350000 - Ammortamenti e Svalutazioni</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>380000</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Oneri Finanziari</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>380000 - Oneri Finanziari</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>390000</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Imposte sul Reddito</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>390000 - Imposte sul Reddito</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>410010</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Vendite Italia</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>410010 - Vendite Italia</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>410020</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Vendite Estero</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>410020 - Vendite Estero</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>430000</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Altri Ricavi e Proventi</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>430000 - Altri Ricavi e Proventi</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>440000</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Proventi Finanziari</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>440000 - Proventi Finanziari</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Konto-Nummer</t>
+          <t>Lieferant (Name oder MwSt-Nr)</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Bezeichnung</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Dropdown (Wird automatisch erstellt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8">
-        <f>IF(A8&lt;&gt;"", A8 &amp; " - " &amp; B8, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="C9">
-        <f>IF(A9&lt;&gt;"", A9 &amp; " - " &amp; B9, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10">
-        <f>IF(A10&lt;&gt;"", A10 &amp; " - " &amp; B10, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11">
-        <f>IF(A11&lt;&gt;"", A11 &amp; " - " &amp; B11, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12">
-        <f>IF(A12&lt;&gt;"", A12 &amp; " - " &amp; B12, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13">
-        <f>IF(A13&lt;&gt;"", A13 &amp; " - " &amp; B13, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14">
-        <f>IF(A14&lt;&gt;"", A14 &amp; " - " &amp; B14, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15">
-        <f>IF(A15&lt;&gt;"", A15 &amp; " - " &amp; B15, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16">
-        <f>IF(A16&lt;&gt;"", A16 &amp; " - " &amp; B16, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17">
-        <f>IF(A17&lt;&gt;"", A17 &amp; " - " &amp; B17, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18">
-        <f>IF(A18&lt;&gt;"", A18 &amp; " - " &amp; B18, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19">
-        <f>IF(A19&lt;&gt;"", A19 &amp; " - " &amp; B19, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20">
-        <f>IF(A20&lt;&gt;"", A20 &amp; " - " &amp; B20, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21">
-        <f>IF(A21&lt;&gt;"", A21 &amp; " - " &amp; B21, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22">
-        <f>IF(A22&lt;&gt;"", A22 &amp; " - " &amp; B22, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23">
-        <f>IF(A23&lt;&gt;"", A23 &amp; " - " &amp; B23, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24">
-        <f>IF(A24&lt;&gt;"", A24 &amp; " - " &amp; B24, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25">
-        <f>IF(A25&lt;&gt;"", A25 &amp; " - " &amp; B25, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26">
-        <f>IF(A26&lt;&gt;"", A26 &amp; " - " &amp; B26, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27">
-        <f>IF(A27&lt;&gt;"", A27 &amp; " - " &amp; B27, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28">
-        <f>IF(A28&lt;&gt;"", A28 &amp; " - " &amp; B28, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29">
-        <f>IF(A29&lt;&gt;"", A29 &amp; " - " &amp; B29, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30">
-        <f>IF(A30&lt;&gt;"", A30 &amp; " - " &amp; B30, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31">
-        <f>IF(A31&lt;&gt;"", A31 &amp; " - " &amp; B31, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32">
-        <f>IF(A32&lt;&gt;"", A32 &amp; " - " &amp; B32, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33">
-        <f>IF(A33&lt;&gt;"", A33 &amp; " - " &amp; B33, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34">
-        <f>IF(A34&lt;&gt;"", A34 &amp; " - " &amp; B34, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35">
-        <f>IF(A35&lt;&gt;"", A35 &amp; " - " &amp; B35, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36">
-        <f>IF(A36&lt;&gt;"", A36 &amp; " - " &amp; B36, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37">
-        <f>IF(A37&lt;&gt;"", A37 &amp; " - " &amp; B37, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38">
-        <f>IF(A38&lt;&gt;"", A38 &amp; " - " &amp; B38, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39">
-        <f>IF(A39&lt;&gt;"", A39 &amp; " - " &amp; B39, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40">
-        <f>IF(A40&lt;&gt;"", A40 &amp; " - " &amp; B40, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41">
-        <f>IF(A41&lt;&gt;"", A41 &amp; " - " &amp; B41, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42">
-        <f>IF(A42&lt;&gt;"", A42 &amp; " - " &amp; B42, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43">
-        <f>IF(A43&lt;&gt;"", A43 &amp; " - " &amp; B43, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44">
-        <f>IF(A44&lt;&gt;"", A44 &amp; " - " &amp; B44, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45">
-        <f>IF(A45&lt;&gt;"", A45 &amp; " - " &amp; B45, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46">
-        <f>IF(A46&lt;&gt;"", A46 &amp; " - " &amp; B46, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47">
-        <f>IF(A47&lt;&gt;"", A47 &amp; " - " &amp; B47, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48">
-        <f>IF(A48&lt;&gt;"", A48 &amp; " - " &amp; B48, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49">
-        <f>IF(A49&lt;&gt;"", A49 &amp; " - " &amp; B49, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50">
-        <f>IF(A50&lt;&gt;"", A50 &amp; " - " &amp; B50, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51">
-        <f>IF(A51&lt;&gt;"", A51 &amp; " - " &amp; B51, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52">
-        <f>IF(A52&lt;&gt;"", A52 &amp; " - " &amp; B52, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53">
-        <f>IF(A53&lt;&gt;"", A53 &amp; " - " &amp; B53, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54">
-        <f>IF(A54&lt;&gt;"", A54 &amp; " - " &amp; B54, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55">
-        <f>IF(A55&lt;&gt;"", A55 &amp; " - " &amp; B55, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56">
-        <f>IF(A56&lt;&gt;"", A56 &amp; " - " &amp; B56, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57">
-        <f>IF(A57&lt;&gt;"", A57 &amp; " - " &amp; B57, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58">
-        <f>IF(A58&lt;&gt;"", A58 &amp; " - " &amp; B58, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59">
-        <f>IF(A59&lt;&gt;"", A59 &amp; " - " &amp; B59, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60">
-        <f>IF(A60&lt;&gt;"", A60 &amp; " - " &amp; B60, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61">
-        <f>IF(A61&lt;&gt;"", A61 &amp; " - " &amp; B61, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62">
-        <f>IF(A62&lt;&gt;"", A62 &amp; " - " &amp; B62, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="C63">
-        <f>IF(A63&lt;&gt;"", A63 &amp; " - " &amp; B63, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="C64">
-        <f>IF(A64&lt;&gt;"", A64 &amp; " - " &amp; B64, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65">
-        <f>IF(A65&lt;&gt;"", A65 &amp; " - " &amp; B65, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="C66">
-        <f>IF(A66&lt;&gt;"", A66 &amp; " - " &amp; B66, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="C67">
-        <f>IF(A67&lt;&gt;"", A67 &amp; " - " &amp; B67, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="C68">
-        <f>IF(A68&lt;&gt;"", A68 &amp; " - " &amp; B68, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="C69">
-        <f>IF(A69&lt;&gt;"", A69 &amp; " - " &amp; B69, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="C70">
-        <f>IF(A70&lt;&gt;"", A70 &amp; " - " &amp; B70, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="C71">
-        <f>IF(A71&lt;&gt;"", A71 &amp; " - " &amp; B71, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="C72">
-        <f>IF(A72&lt;&gt;"", A72 &amp; " - " &amp; B72, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="C73">
-        <f>IF(A73&lt;&gt;"", A73 &amp; " - " &amp; B73, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="C74">
-        <f>IF(A74&lt;&gt;"", A74 &amp; " - " &amp; B74, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="C75">
-        <f>IF(A75&lt;&gt;"", A75 &amp; " - " &amp; B75, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="C76">
-        <f>IF(A76&lt;&gt;"", A76 &amp; " - " &amp; B76, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="C77">
-        <f>IF(A77&lt;&gt;"", A77 &amp; " - " &amp; B77, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="C78">
-        <f>IF(A78&lt;&gt;"", A78 &amp; " - " &amp; B78, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="C79">
-        <f>IF(A79&lt;&gt;"", A79 &amp; " - " &amp; B79, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="C80">
-        <f>IF(A80&lt;&gt;"", A80 &amp; " - " &amp; B80, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="C81">
-        <f>IF(A81&lt;&gt;"", A81 &amp; " - " &amp; B81, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="C82">
-        <f>IF(A82&lt;&gt;"", A82 &amp; " - " &amp; B82, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="C83">
-        <f>IF(A83&lt;&gt;"", A83 &amp; " - " &amp; B83, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="C84">
-        <f>IF(A84&lt;&gt;"", A84 &amp; " - " &amp; B84, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="C85">
-        <f>IF(A85&lt;&gt;"", A85 &amp; " - " &amp; B85, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="C86">
-        <f>IF(A86&lt;&gt;"", A86 &amp; " - " &amp; B86, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="C87">
-        <f>IF(A87&lt;&gt;"", A87 &amp; " - " &amp; B87, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="C88">
-        <f>IF(A88&lt;&gt;"", A88 &amp; " - " &amp; B88, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="C89">
-        <f>IF(A89&lt;&gt;"", A89 &amp; " - " &amp; B89, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="C90">
-        <f>IF(A90&lt;&gt;"", A90 &amp; " - " &amp; B90, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="C91">
-        <f>IF(A91&lt;&gt;"", A91 &amp; " - " &amp; B91, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="C92">
-        <f>IF(A92&lt;&gt;"", A92 &amp; " - " &amp; B92, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="C93">
-        <f>IF(A93&lt;&gt;"", A93 &amp; " - " &amp; B93, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="C94">
-        <f>IF(A94&lt;&gt;"", A94 &amp; " - " &amp; B94, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="C95">
-        <f>IF(A95&lt;&gt;"", A95 &amp; " - " &amp; B95, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="C96">
-        <f>IF(A96&lt;&gt;"", A96 &amp; " - " &amp; B96, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="C97">
-        <f>IF(A97&lt;&gt;"", A97 &amp; " - " &amp; B97, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="C98">
-        <f>IF(A98&lt;&gt;"", A98 &amp; " - " &amp; B98, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="C99">
-        <f>IF(A99&lt;&gt;"", A99 &amp; " - " &amp; B99, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="C100">
-        <f>IF(A100&lt;&gt;"", A100 &amp; " - " &amp; B100, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="C101">
-        <f>IF(A101&lt;&gt;"", A101 &amp; " - " &amp; B101, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="C102">
-        <f>IF(A102&lt;&gt;"", A102 &amp; " - " &amp; B102, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="C103">
-        <f>IF(A103&lt;&gt;"", A103 &amp; " - " &amp; B103, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="C104">
-        <f>IF(A104&lt;&gt;"", A104 &amp; " - " &amp; B104, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="C105">
-        <f>IF(A105&lt;&gt;"", A105 &amp; " - " &amp; B105, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="C106">
-        <f>IF(A106&lt;&gt;"", A106 &amp; " - " &amp; B106, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="C107">
-        <f>IF(A107&lt;&gt;"", A107 &amp; " - " &amp; B107, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="C108">
-        <f>IF(A108&lt;&gt;"", A108 &amp; " - " &amp; B108, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="C109">
-        <f>IF(A109&lt;&gt;"", A109 &amp; " - " &amp; B109, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="C110">
-        <f>IF(A110&lt;&gt;"", A110 &amp; " - " &amp; B110, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="C111">
-        <f>IF(A111&lt;&gt;"", A111 &amp; " - " &amp; B111, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="C112">
-        <f>IF(A112&lt;&gt;"", A112 &amp; " - " &amp; B112, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="C113">
-        <f>IF(A113&lt;&gt;"", A113 &amp; " - " &amp; B113, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="C114">
-        <f>IF(A114&lt;&gt;"", A114 &amp; " - " &amp; B114, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="C115">
-        <f>IF(A115&lt;&gt;"", A115 &amp; " - " &amp; B115, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="C116">
-        <f>IF(A116&lt;&gt;"", A116 &amp; " - " &amp; B116, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="C117">
-        <f>IF(A117&lt;&gt;"", A117 &amp; " - " &amp; B117, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="C118">
-        <f>IF(A118&lt;&gt;"", A118 &amp; " - " &amp; B118, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="C119">
-        <f>IF(A119&lt;&gt;"", A119 &amp; " - " &amp; B119, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="C120">
-        <f>IF(A120&lt;&gt;"", A120 &amp; " - " &amp; B120, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="C121">
-        <f>IF(A121&lt;&gt;"", A121 &amp; " - " &amp; B121, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="C122">
-        <f>IF(A122&lt;&gt;"", A122 &amp; " - " &amp; B122, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="C123">
-        <f>IF(A123&lt;&gt;"", A123 &amp; " - " &amp; B123, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="C124">
-        <f>IF(A124&lt;&gt;"", A124 &amp; " - " &amp; B124, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="C125">
-        <f>IF(A125&lt;&gt;"", A125 &amp; " - " &amp; B125, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="C126">
-        <f>IF(A126&lt;&gt;"", A126 &amp; " - " &amp; B126, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="C127">
-        <f>IF(A127&lt;&gt;"", A127 &amp; " - " &amp; B127, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="C128">
-        <f>IF(A128&lt;&gt;"", A128 &amp; " - " &amp; B128, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="C129">
-        <f>IF(A129&lt;&gt;"", A129 &amp; " - " &amp; B129, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="C130">
-        <f>IF(A130&lt;&gt;"", A130 &amp; " - " &amp; B130, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="C131">
-        <f>IF(A131&lt;&gt;"", A131 &amp; " - " &amp; B131, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="C132">
-        <f>IF(A132&lt;&gt;"", A132 &amp; " - " &amp; B132, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="C133">
-        <f>IF(A133&lt;&gt;"", A133 &amp; " - " &amp; B133, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="C134">
-        <f>IF(A134&lt;&gt;"", A134 &amp; " - " &amp; B134, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="C135">
-        <f>IF(A135&lt;&gt;"", A135 &amp; " - " &amp; B135, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="C136">
-        <f>IF(A136&lt;&gt;"", A136 &amp; " - " &amp; B136, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="C137">
-        <f>IF(A137&lt;&gt;"", A137 &amp; " - " &amp; B137, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="C138">
-        <f>IF(A138&lt;&gt;"", A138 &amp; " - " &amp; B138, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="C139">
-        <f>IF(A139&lt;&gt;"", A139 &amp; " - " &amp; B139, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="C140">
-        <f>IF(A140&lt;&gt;"", A140 &amp; " - " &amp; B140, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="C141">
-        <f>IF(A141&lt;&gt;"", A141 &amp; " - " &amp; B141, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142">
-        <f>IF(A142&lt;&gt;"", A142 &amp; " - " &amp; B142, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="C143">
-        <f>IF(A143&lt;&gt;"", A143 &amp; " - " &amp; B143, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="C144">
-        <f>IF(A144&lt;&gt;"", A144 &amp; " - " &amp; B144, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="C145">
-        <f>IF(A145&lt;&gt;"", A145 &amp; " - " &amp; B145, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="C146">
-        <f>IF(A146&lt;&gt;"", A146 &amp; " - " &amp; B146, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="C147">
-        <f>IF(A147&lt;&gt;"", A147 &amp; " - " &amp; B147, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="C148">
-        <f>IF(A148&lt;&gt;"", A148 &amp; " - " &amp; B148, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="C149">
-        <f>IF(A149&lt;&gt;"", A149 &amp; " - " &amp; B149, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="C150">
-        <f>IF(A150&lt;&gt;"", A150 &amp; " - " &amp; B150, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="C151">
-        <f>IF(A151&lt;&gt;"", A151 &amp; " - " &amp; B151, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="C152">
-        <f>IF(A152&lt;&gt;"", A152 &amp; " - " &amp; B152, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="C153">
-        <f>IF(A153&lt;&gt;"", A153 &amp; " - " &amp; B153, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="C154">
-        <f>IF(A154&lt;&gt;"", A154 &amp; " - " &amp; B154, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="C155">
-        <f>IF(A155&lt;&gt;"", A155 &amp; " - " &amp; B155, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="C156">
-        <f>IF(A156&lt;&gt;"", A156 &amp; " - " &amp; B156, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="C157">
-        <f>IF(A157&lt;&gt;"", A157 &amp; " - " &amp; B157, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="C158">
-        <f>IF(A158&lt;&gt;"", A158 &amp; " - " &amp; B158, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="C159">
-        <f>IF(A159&lt;&gt;"", A159 &amp; " - " &amp; B159, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="C160">
-        <f>IF(A160&lt;&gt;"", A160 &amp; " - " &amp; B160, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="C161">
-        <f>IF(A161&lt;&gt;"", A161 &amp; " - " &amp; B161, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="C162">
-        <f>IF(A162&lt;&gt;"", A162 &amp; " - " &amp; B162, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="C163">
-        <f>IF(A163&lt;&gt;"", A163 &amp; " - " &amp; B163, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="C164">
-        <f>IF(A164&lt;&gt;"", A164 &amp; " - " &amp; B164, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="C165">
-        <f>IF(A165&lt;&gt;"", A165 &amp; " - " &amp; B165, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="C166">
-        <f>IF(A166&lt;&gt;"", A166 &amp; " - " &amp; B166, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="C167">
-        <f>IF(A167&lt;&gt;"", A167 &amp; " - " &amp; B167, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="C168">
-        <f>IF(A168&lt;&gt;"", A168 &amp; " - " &amp; B168, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="C169">
-        <f>IF(A169&lt;&gt;"", A169 &amp; " - " &amp; B169, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="C170">
-        <f>IF(A170&lt;&gt;"", A170 &amp; " - " &amp; B170, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="C171">
-        <f>IF(A171&lt;&gt;"", A171 &amp; " - " &amp; B171, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="C172">
-        <f>IF(A172&lt;&gt;"", A172 &amp; " - " &amp; B172, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="C173">
-        <f>IF(A173&lt;&gt;"", A173 &amp; " - " &amp; B173, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="C174">
-        <f>IF(A174&lt;&gt;"", A174 &amp; " - " &amp; B174, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="C175">
-        <f>IF(A175&lt;&gt;"", A175 &amp; " - " &amp; B175, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="C176">
-        <f>IF(A176&lt;&gt;"", A176 &amp; " - " &amp; B176, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="C177">
-        <f>IF(A177&lt;&gt;"", A177 &amp; " - " &amp; B177, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="C178">
-        <f>IF(A178&lt;&gt;"", A178 &amp; " - " &amp; B178, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="C179">
-        <f>IF(A179&lt;&gt;"", A179 &amp; " - " &amp; B179, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="C180">
-        <f>IF(A180&lt;&gt;"", A180 &amp; " - " &amp; B180, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="C181">
-        <f>IF(A181&lt;&gt;"", A181 &amp; " - " &amp; B181, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="C182">
-        <f>IF(A182&lt;&gt;"", A182 &amp; " - " &amp; B182, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="C183">
-        <f>IF(A183&lt;&gt;"", A183 &amp; " - " &amp; B183, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="C184">
-        <f>IF(A184&lt;&gt;"", A184 &amp; " - " &amp; B184, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="C185">
-        <f>IF(A185&lt;&gt;"", A185 &amp; " - " &amp; B185, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="C186">
-        <f>IF(A186&lt;&gt;"", A186 &amp; " - " &amp; B186, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="C187">
-        <f>IF(A187&lt;&gt;"", A187 &amp; " - " &amp; B187, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="C188">
-        <f>IF(A188&lt;&gt;"", A188 &amp; " - " &amp; B188, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="C189">
-        <f>IF(A189&lt;&gt;"", A189 &amp; " - " &amp; B189, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="C190">
-        <f>IF(A190&lt;&gt;"", A190 &amp; " - " &amp; B190, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="C191">
-        <f>IF(A191&lt;&gt;"", A191 &amp; " - " &amp; B191, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="C192">
-        <f>IF(A192&lt;&gt;"", A192 &amp; " - " &amp; B192, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="C193">
-        <f>IF(A193&lt;&gt;"", A193 &amp; " - " &amp; B193, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="C194">
-        <f>IF(A194&lt;&gt;"", A194 &amp; " - " &amp; B194, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="C195">
-        <f>IF(A195&lt;&gt;"", A195 &amp; " - " &amp; B195, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="C196">
-        <f>IF(A196&lt;&gt;"", A196 &amp; " - " &amp; B196, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="C197">
-        <f>IF(A197&lt;&gt;"", A197 &amp; " - " &amp; B197, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="C198">
-        <f>IF(A198&lt;&gt;"", A198 &amp; " - " &amp; B198, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="C199">
-        <f>IF(A199&lt;&gt;"", A199 &amp; " - " &amp; B199, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="C200">
-        <f>IF(A200&lt;&gt;"", A200 &amp; " - " &amp; B200, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="C201">
-        <f>IF(A201&lt;&gt;"", A201 &amp; " - " &amp; B201, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="C202">
-        <f>IF(A202&lt;&gt;"", A202 &amp; " - " &amp; B202, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="C203">
-        <f>IF(A203&lt;&gt;"", A203 &amp; " - " &amp; B203, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="C204">
-        <f>IF(A204&lt;&gt;"", A204 &amp; " - " &amp; B204, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="C205">
-        <f>IF(A205&lt;&gt;"", A205 &amp; " - " &amp; B205, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="C206">
-        <f>IF(A206&lt;&gt;"", A206 &amp; " - " &amp; B206, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="C207">
-        <f>IF(A207&lt;&gt;"", A207 &amp; " - " &amp; B207, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="C208">
-        <f>IF(A208&lt;&gt;"", A208 &amp; " - " &amp; B208, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="C209">
-        <f>IF(A209&lt;&gt;"", A209 &amp; " - " &amp; B209, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="C210">
-        <f>IF(A210&lt;&gt;"", A210 &amp; " - " &amp; B210, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="C211">
-        <f>IF(A211&lt;&gt;"", A211 &amp; " - " &amp; B211, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="C212">
-        <f>IF(A212&lt;&gt;"", A212 &amp; " - " &amp; B212, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="C213">
-        <f>IF(A213&lt;&gt;"", A213 &amp; " - " &amp; B213, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="C214">
-        <f>IF(A214&lt;&gt;"", A214 &amp; " - " &amp; B214, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="C215">
-        <f>IF(A215&lt;&gt;"", A215 &amp; " - " &amp; B215, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="C216">
-        <f>IF(A216&lt;&gt;"", A216 &amp; " - " &amp; B216, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="C217">
-        <f>IF(A217&lt;&gt;"", A217 &amp; " - " &amp; B217, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="C218">
-        <f>IF(A218&lt;&gt;"", A218 &amp; " - " &amp; B218, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="C219">
-        <f>IF(A219&lt;&gt;"", A219 &amp; " - " &amp; B219, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="C220">
-        <f>IF(A220&lt;&gt;"", A220 &amp; " - " &amp; B220, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="C221">
-        <f>IF(A221&lt;&gt;"", A221 &amp; " - " &amp; B221, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="C222">
-        <f>IF(A222&lt;&gt;"", A222 &amp; " - " &amp; B222, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="C223">
-        <f>IF(A223&lt;&gt;"", A223 &amp; " - " &amp; B223, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="C224">
-        <f>IF(A224&lt;&gt;"", A224 &amp; " - " &amp; B224, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="C225">
-        <f>IF(A225&lt;&gt;"", A225 &amp; " - " &amp; B225, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226">
-      <c r="C226">
-        <f>IF(A226&lt;&gt;"", A226 &amp; " - " &amp; B226, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="C227">
-        <f>IF(A227&lt;&gt;"", A227 &amp; " - " &amp; B227, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="C228">
-        <f>IF(A228&lt;&gt;"", A228 &amp; " - " &amp; B228, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="C229">
-        <f>IF(A229&lt;&gt;"", A229 &amp; " - " &amp; B229, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="C230">
-        <f>IF(A230&lt;&gt;"", A230 &amp; " - " &amp; B230, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="C231">
-        <f>IF(A231&lt;&gt;"", A231 &amp; " - " &amp; B231, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="C232">
-        <f>IF(A232&lt;&gt;"", A232 &amp; " - " &amp; B232, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="C233">
-        <f>IF(A233&lt;&gt;"", A233 &amp; " - " &amp; B233, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="C234">
-        <f>IF(A234&lt;&gt;"", A234 &amp; " - " &amp; B234, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="C235">
-        <f>IF(A235&lt;&gt;"", A235 &amp; " - " &amp; B235, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="C236">
-        <f>IF(A236&lt;&gt;"", A236 &amp; " - " &amp; B236, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="C237">
-        <f>IF(A237&lt;&gt;"", A237 &amp; " - " &amp; B237, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="C238">
-        <f>IF(A238&lt;&gt;"", A238 &amp; " - " &amp; B238, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="C239">
-        <f>IF(A239&lt;&gt;"", A239 &amp; " - " &amp; B239, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="C240">
-        <f>IF(A240&lt;&gt;"", A240 &amp; " - " &amp; B240, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="C241">
-        <f>IF(A241&lt;&gt;"", A241 &amp; " - " &amp; B241, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="C242">
-        <f>IF(A242&lt;&gt;"", A242 &amp; " - " &amp; B242, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="C243">
-        <f>IF(A243&lt;&gt;"", A243 &amp; " - " &amp; B243, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="C244">
-        <f>IF(A244&lt;&gt;"", A244 &amp; " - " &amp; B244, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="C245">
-        <f>IF(A245&lt;&gt;"", A245 &amp; " - " &amp; B245, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="C246">
-        <f>IF(A246&lt;&gt;"", A246 &amp; " - " &amp; B246, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="C247">
-        <f>IF(A247&lt;&gt;"", A247 &amp; " - " &amp; B247, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="C248">
-        <f>IF(A248&lt;&gt;"", A248 &amp; " - " &amp; B248, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="C249">
-        <f>IF(A249&lt;&gt;"", A249 &amp; " - " &amp; B249, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="C250">
-        <f>IF(A250&lt;&gt;"", A250 &amp; " - " &amp; B250, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="C251">
-        <f>IF(A251&lt;&gt;"", A251 &amp; " - " &amp; B251, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="C252">
-        <f>IF(A252&lt;&gt;"", A252 &amp; " - " &amp; B252, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="C253">
-        <f>IF(A253&lt;&gt;"", A253 &amp; " - " &amp; B253, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="C254">
-        <f>IF(A254&lt;&gt;"", A254 &amp; " - " &amp; B254, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="C255">
-        <f>IF(A255&lt;&gt;"", A255 &amp; " - " &amp; B255, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="C256">
-        <f>IF(A256&lt;&gt;"", A256 &amp; " - " &amp; B256, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="C257">
-        <f>IF(A257&lt;&gt;"", A257 &amp; " - " &amp; B257, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="C258">
-        <f>IF(A258&lt;&gt;"", A258 &amp; " - " &amp; B258, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="C259">
-        <f>IF(A259&lt;&gt;"", A259 &amp; " - " &amp; B259, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="C260">
-        <f>IF(A260&lt;&gt;"", A260 &amp; " - " &amp; B260, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="C261">
-        <f>IF(A261&lt;&gt;"", A261 &amp; " - " &amp; B261, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="C262">
-        <f>IF(A262&lt;&gt;"", A262 &amp; " - " &amp; B262, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="C263">
-        <f>IF(A263&lt;&gt;"", A263 &amp; " - " &amp; B263, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="C264">
-        <f>IF(A264&lt;&gt;"", A264 &amp; " - " &amp; B264, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="C265">
-        <f>IF(A265&lt;&gt;"", A265 &amp; " - " &amp; B265, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266">
-      <c r="C266">
-        <f>IF(A266&lt;&gt;"", A266 &amp; " - " &amp; B266, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267">
-      <c r="C267">
-        <f>IF(A267&lt;&gt;"", A267 &amp; " - " &amp; B267, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="C268">
-        <f>IF(A268&lt;&gt;"", A268 &amp; " - " &amp; B268, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="C269">
-        <f>IF(A269&lt;&gt;"", A269 &amp; " - " &amp; B269, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="C270">
-        <f>IF(A270&lt;&gt;"", A270 &amp; " - " &amp; B270, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="C271">
-        <f>IF(A271&lt;&gt;"", A271 &amp; " - " &amp; B271, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="C272">
-        <f>IF(A272&lt;&gt;"", A272 &amp; " - " &amp; B272, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="C273">
-        <f>IF(A273&lt;&gt;"", A273 &amp; " - " &amp; B273, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="C274">
-        <f>IF(A274&lt;&gt;"", A274 &amp; " - " &amp; B274, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="C275">
-        <f>IF(A275&lt;&gt;"", A275 &amp; " - " &amp; B275, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276">
-      <c r="C276">
-        <f>IF(A276&lt;&gt;"", A276 &amp; " - " &amp; B276, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="C277">
-        <f>IF(A277&lt;&gt;"", A277 &amp; " - " &amp; B277, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278">
-      <c r="C278">
-        <f>IF(A278&lt;&gt;"", A278 &amp; " - " &amp; B278, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279">
-      <c r="C279">
-        <f>IF(A279&lt;&gt;"", A279 &amp; " - " &amp; B279, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280">
-      <c r="C280">
-        <f>IF(A280&lt;&gt;"", A280 &amp; " - " &amp; B280, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="C281">
-        <f>IF(A281&lt;&gt;"", A281 &amp; " - " &amp; B281, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="C282">
-        <f>IF(A282&lt;&gt;"", A282 &amp; " - " &amp; B282, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283">
-      <c r="C283">
-        <f>IF(A283&lt;&gt;"", A283 &amp; " - " &amp; B283, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284">
-      <c r="C284">
-        <f>IF(A284&lt;&gt;"", A284 &amp; " - " &amp; B284, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285">
-      <c r="C285">
-        <f>IF(A285&lt;&gt;"", A285 &amp; " - " &amp; B285, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286">
-      <c r="C286">
-        <f>IF(A286&lt;&gt;"", A286 &amp; " - " &amp; B286, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287">
-      <c r="C287">
-        <f>IF(A287&lt;&gt;"", A287 &amp; " - " &amp; B287, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288">
-      <c r="C288">
-        <f>IF(A288&lt;&gt;"", A288 &amp; " - " &amp; B288, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289">
-      <c r="C289">
-        <f>IF(A289&lt;&gt;"", A289 &amp; " - " &amp; B289, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290">
-      <c r="C290">
-        <f>IF(A290&lt;&gt;"", A290 &amp; " - " &amp; B290, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291">
-      <c r="C291">
-        <f>IF(A291&lt;&gt;"", A291 &amp; " - " &amp; B291, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292">
-      <c r="C292">
-        <f>IF(A292&lt;&gt;"", A292 &amp; " - " &amp; B292, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293">
-      <c r="C293">
-        <f>IF(A293&lt;&gt;"", A293 &amp; " - " &amp; B293, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294">
-      <c r="C294">
-        <f>IF(A294&lt;&gt;"", A294 &amp; " - " &amp; B294, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295">
-      <c r="C295">
-        <f>IF(A295&lt;&gt;"", A295 &amp; " - " &amp; B295, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296">
-      <c r="C296">
-        <f>IF(A296&lt;&gt;"", A296 &amp; " - " &amp; B296, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297">
-      <c r="C297">
-        <f>IF(A297&lt;&gt;"", A297 &amp; " - " &amp; B297, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298">
-      <c r="C298">
-        <f>IF(A298&lt;&gt;"", A298 &amp; " - " &amp; B298, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299">
-      <c r="C299">
-        <f>IF(A299&lt;&gt;"", A299 &amp; " - " &amp; B299, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300">
-      <c r="C300">
-        <f>IF(A300&lt;&gt;"", A300 &amp; " - " &amp; B300, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301">
-      <c r="C301">
-        <f>IF(A301&lt;&gt;"", A301 &amp; " - " &amp; B301, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302">
-      <c r="C302">
-        <f>IF(A302&lt;&gt;"", A302 &amp; " - " &amp; B302, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303">
-      <c r="C303">
-        <f>IF(A303&lt;&gt;"", A303 &amp; " - " &amp; B303, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304">
-      <c r="C304">
-        <f>IF(A304&lt;&gt;"", A304 &amp; " - " &amp; B304, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305">
-      <c r="C305">
-        <f>IF(A305&lt;&gt;"", A305 &amp; " - " &amp; B305, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="306">
-      <c r="C306">
-        <f>IF(A306&lt;&gt;"", A306 &amp; " - " &amp; B306, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307">
-      <c r="C307">
-        <f>IF(A307&lt;&gt;"", A307 &amp; " - " &amp; B307, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="308">
-      <c r="C308">
-        <f>IF(A308&lt;&gt;"", A308 &amp; " - " &amp; B308, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="309">
-      <c r="C309">
-        <f>IF(A309&lt;&gt;"", A309 &amp; " - " &amp; B309, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310">
-      <c r="C310">
-        <f>IF(A310&lt;&gt;"", A310 &amp; " - " &amp; B310, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311">
-      <c r="C311">
-        <f>IF(A311&lt;&gt;"", A311 &amp; " - " &amp; B311, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="C312">
-        <f>IF(A312&lt;&gt;"", A312 &amp; " - " &amp; B312, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313">
-      <c r="C313">
-        <f>IF(A313&lt;&gt;"", A313 &amp; " - " &amp; B313, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314">
-      <c r="C314">
-        <f>IF(A314&lt;&gt;"", A314 &amp; " - " &amp; B314, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315">
-      <c r="C315">
-        <f>IF(A315&lt;&gt;"", A315 &amp; " - " &amp; B315, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316">
-      <c r="C316">
-        <f>IF(A316&lt;&gt;"", A316 &amp; " - " &amp; B316, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="C317">
-        <f>IF(A317&lt;&gt;"", A317 &amp; " - " &amp; B317, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318">
-      <c r="C318">
-        <f>IF(A318&lt;&gt;"", A318 &amp; " - " &amp; B318, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319">
-      <c r="C319">
-        <f>IF(A319&lt;&gt;"", A319 &amp; " - " &amp; B319, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="320">
-      <c r="C320">
-        <f>IF(A320&lt;&gt;"", A320 &amp; " - " &amp; B320, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321">
-      <c r="C321">
-        <f>IF(A321&lt;&gt;"", A321 &amp; " - " &amp; B321, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322">
-      <c r="C322">
-        <f>IF(A322&lt;&gt;"", A322 &amp; " - " &amp; B322, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="323">
-      <c r="C323">
-        <f>IF(A323&lt;&gt;"", A323 &amp; " - " &amp; B323, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324">
-      <c r="C324">
-        <f>IF(A324&lt;&gt;"", A324 &amp; " - " &amp; B324, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="325">
-      <c r="C325">
-        <f>IF(A325&lt;&gt;"", A325 &amp; " - " &amp; B325, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326">
-      <c r="C326">
-        <f>IF(A326&lt;&gt;"", A326 &amp; " - " &amp; B326, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327">
-      <c r="C327">
-        <f>IF(A327&lt;&gt;"", A327 &amp; " - " &amp; B327, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328">
-      <c r="C328">
-        <f>IF(A328&lt;&gt;"", A328 &amp; " - " &amp; B328, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329">
-      <c r="C329">
-        <f>IF(A329&lt;&gt;"", A329 &amp; " - " &amp; B329, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="330">
-      <c r="C330">
-        <f>IF(A330&lt;&gt;"", A330 &amp; " - " &amp; B330, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="331">
-      <c r="C331">
-        <f>IF(A331&lt;&gt;"", A331 &amp; " - " &amp; B331, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="332">
-      <c r="C332">
-        <f>IF(A332&lt;&gt;"", A332 &amp; " - " &amp; B332, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333">
-      <c r="C333">
-        <f>IF(A333&lt;&gt;"", A333 &amp; " - " &amp; B333, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334">
-      <c r="C334">
-        <f>IF(A334&lt;&gt;"", A334 &amp; " - " &amp; B334, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="335">
-      <c r="C335">
-        <f>IF(A335&lt;&gt;"", A335 &amp; " - " &amp; B335, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="C336">
-        <f>IF(A336&lt;&gt;"", A336 &amp; " - " &amp; B336, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337">
-      <c r="C337">
-        <f>IF(A337&lt;&gt;"", A337 &amp; " - " &amp; B337, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338">
-      <c r="C338">
-        <f>IF(A338&lt;&gt;"", A338 &amp; " - " &amp; B338, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339">
-      <c r="C339">
-        <f>IF(A339&lt;&gt;"", A339 &amp; " - " &amp; B339, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="C340">
-        <f>IF(A340&lt;&gt;"", A340 &amp; " - " &amp; B340, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341">
-      <c r="C341">
-        <f>IF(A341&lt;&gt;"", A341 &amp; " - " &amp; B341, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="342">
-      <c r="C342">
-        <f>IF(A342&lt;&gt;"", A342 &amp; " - " &amp; B342, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343">
-      <c r="C343">
-        <f>IF(A343&lt;&gt;"", A343 &amp; " - " &amp; B343, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="344">
-      <c r="C344">
-        <f>IF(A344&lt;&gt;"", A344 &amp; " - " &amp; B344, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345">
-      <c r="C345">
-        <f>IF(A345&lt;&gt;"", A345 &amp; " - " &amp; B345, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="346">
-      <c r="C346">
-        <f>IF(A346&lt;&gt;"", A346 &amp; " - " &amp; B346, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347">
-      <c r="C347">
-        <f>IF(A347&lt;&gt;"", A347 &amp; " - " &amp; B347, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348">
-      <c r="C348">
-        <f>IF(A348&lt;&gt;"", A348 &amp; " - " &amp; B348, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349">
-      <c r="C349">
-        <f>IF(A349&lt;&gt;"", A349 &amp; " - " &amp; B349, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350">
-      <c r="C350">
-        <f>IF(A350&lt;&gt;"", A350 &amp; " - " &amp; B350, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351">
-      <c r="C351">
-        <f>IF(A351&lt;&gt;"", A351 &amp; " - " &amp; B351, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352">
-      <c r="C352">
-        <f>IF(A352&lt;&gt;"", A352 &amp; " - " &amp; B352, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="C353">
-        <f>IF(A353&lt;&gt;"", A353 &amp; " - " &amp; B353, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354">
-      <c r="C354">
-        <f>IF(A354&lt;&gt;"", A354 &amp; " - " &amp; B354, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="355">
-      <c r="C355">
-        <f>IF(A355&lt;&gt;"", A355 &amp; " - " &amp; B355, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="356">
-      <c r="C356">
-        <f>IF(A356&lt;&gt;"", A356 &amp; " - " &amp; B356, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="357">
-      <c r="C357">
-        <f>IF(A357&lt;&gt;"", A357 &amp; " - " &amp; B357, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358">
-      <c r="C358">
-        <f>IF(A358&lt;&gt;"", A358 &amp; " - " &amp; B358, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359">
-      <c r="C359">
-        <f>IF(A359&lt;&gt;"", A359 &amp; " - " &amp; B359, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="360">
-      <c r="C360">
-        <f>IF(A360&lt;&gt;"", A360 &amp; " - " &amp; B360, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="361">
-      <c r="C361">
-        <f>IF(A361&lt;&gt;"", A361 &amp; " - " &amp; B361, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="362">
-      <c r="C362">
-        <f>IF(A362&lt;&gt;"", A362 &amp; " - " &amp; B362, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="363">
-      <c r="C363">
-        <f>IF(A363&lt;&gt;"", A363 &amp; " - " &amp; B363, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="364">
-      <c r="C364">
-        <f>IF(A364&lt;&gt;"", A364 &amp; " - " &amp; B364, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="365">
-      <c r="C365">
-        <f>IF(A365&lt;&gt;"", A365 &amp; " - " &amp; B365, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="C366">
-        <f>IF(A366&lt;&gt;"", A366 &amp; " - " &amp; B366, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367">
-      <c r="C367">
-        <f>IF(A367&lt;&gt;"", A367 &amp; " - " &amp; B367, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="368">
-      <c r="C368">
-        <f>IF(A368&lt;&gt;"", A368 &amp; " - " &amp; B368, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369">
-      <c r="C369">
-        <f>IF(A369&lt;&gt;"", A369 &amp; " - " &amp; B369, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370">
-      <c r="C370">
-        <f>IF(A370&lt;&gt;"", A370 &amp; " - " &amp; B370, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="371">
-      <c r="C371">
-        <f>IF(A371&lt;&gt;"", A371 &amp; " - " &amp; B371, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="372">
-      <c r="C372">
-        <f>IF(A372&lt;&gt;"", A372 &amp; " - " &amp; B372, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="373">
-      <c r="C373">
-        <f>IF(A373&lt;&gt;"", A373 &amp; " - " &amp; B373, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="374">
-      <c r="C374">
-        <f>IF(A374&lt;&gt;"", A374 &amp; " - " &amp; B374, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="375">
-      <c r="C375">
-        <f>IF(A375&lt;&gt;"", A375 &amp; " - " &amp; B375, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="376">
-      <c r="C376">
-        <f>IF(A376&lt;&gt;"", A376 &amp; " - " &amp; B376, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="377">
-      <c r="C377">
-        <f>IF(A377&lt;&gt;"", A377 &amp; " - " &amp; B377, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="378">
-      <c r="C378">
-        <f>IF(A378&lt;&gt;"", A378 &amp; " - " &amp; B378, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="C379">
-        <f>IF(A379&lt;&gt;"", A379 &amp; " - " &amp; B379, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380">
-      <c r="C380">
-        <f>IF(A380&lt;&gt;"", A380 &amp; " - " &amp; B380, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="381">
-      <c r="C381">
-        <f>IF(A381&lt;&gt;"", A381 &amp; " - " &amp; B381, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="382">
-      <c r="C382">
-        <f>IF(A382&lt;&gt;"", A382 &amp; " - " &amp; B382, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="383">
-      <c r="C383">
-        <f>IF(A383&lt;&gt;"", A383 &amp; " - " &amp; B383, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="384">
-      <c r="C384">
-        <f>IF(A384&lt;&gt;"", A384 &amp; " - " &amp; B384, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="385">
-      <c r="C385">
-        <f>IF(A385&lt;&gt;"", A385 &amp; " - " &amp; B385, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="386">
-      <c r="C386">
-        <f>IF(A386&lt;&gt;"", A386 &amp; " - " &amp; B386, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="387">
-      <c r="C387">
-        <f>IF(A387&lt;&gt;"", A387 &amp; " - " &amp; B387, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388">
-      <c r="C388">
-        <f>IF(A388&lt;&gt;"", A388 &amp; " - " &amp; B388, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="389">
-      <c r="C389">
-        <f>IF(A389&lt;&gt;"", A389 &amp; " - " &amp; B389, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390">
-      <c r="C390">
-        <f>IF(A390&lt;&gt;"", A390 &amp; " - " &amp; B390, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="391">
-      <c r="C391">
-        <f>IF(A391&lt;&gt;"", A391 &amp; " - " &amp; B391, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="C392">
-        <f>IF(A392&lt;&gt;"", A392 &amp; " - " &amp; B392, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393">
-      <c r="C393">
-        <f>IF(A393&lt;&gt;"", A393 &amp; " - " &amp; B393, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="394">
-      <c r="C394">
-        <f>IF(A394&lt;&gt;"", A394 &amp; " - " &amp; B394, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="395">
-      <c r="C395">
-        <f>IF(A395&lt;&gt;"", A395 &amp; " - " &amp; B395, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="396">
-      <c r="C396">
-        <f>IF(A396&lt;&gt;"", A396 &amp; " - " &amp; B396, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="397">
-      <c r="C397">
-        <f>IF(A397&lt;&gt;"", A397 &amp; " - " &amp; B397, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="398">
-      <c r="C398">
-        <f>IF(A398&lt;&gt;"", A398 &amp; " - " &amp; B398, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="399">
-      <c r="C399">
-        <f>IF(A399&lt;&gt;"", A399 &amp; " - " &amp; B399, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="400">
-      <c r="C400">
-        <f>IF(A400&lt;&gt;"", A400 &amp; " - " &amp; B400, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="401">
-      <c r="C401">
-        <f>IF(A401&lt;&gt;"", A401 &amp; " - " &amp; B401, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="402">
-      <c r="C402">
-        <f>IF(A402&lt;&gt;"", A402 &amp; " - " &amp; B402, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="403">
-      <c r="C403">
-        <f>IF(A403&lt;&gt;"", A403 &amp; " - " &amp; B403, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="404">
-      <c r="C404">
-        <f>IF(A404&lt;&gt;"", A404 &amp; " - " &amp; B404, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="C405">
-        <f>IF(A405&lt;&gt;"", A405 &amp; " - " &amp; B405, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406">
-      <c r="C406">
-        <f>IF(A406&lt;&gt;"", A406 &amp; " - " &amp; B406, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="407">
-      <c r="C407">
-        <f>IF(A407&lt;&gt;"", A407 &amp; " - " &amp; B407, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="408">
-      <c r="C408">
-        <f>IF(A408&lt;&gt;"", A408 &amp; " - " &amp; B408, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="409">
-      <c r="C409">
-        <f>IF(A409&lt;&gt;"", A409 &amp; " - " &amp; B409, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="410">
-      <c r="C410">
-        <f>IF(A410&lt;&gt;"", A410 &amp; " - " &amp; B410, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="411">
-      <c r="C411">
-        <f>IF(A411&lt;&gt;"", A411 &amp; " - " &amp; B411, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="412">
-      <c r="C412">
-        <f>IF(A412&lt;&gt;"", A412 &amp; " - " &amp; B412, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="413">
-      <c r="C413">
-        <f>IF(A413&lt;&gt;"", A413 &amp; " - " &amp; B413, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="414">
-      <c r="C414">
-        <f>IF(A414&lt;&gt;"", A414 &amp; " - " &amp; B414, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="415">
-      <c r="C415">
-        <f>IF(A415&lt;&gt;"", A415 &amp; " - " &amp; B415, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="416">
-      <c r="C416">
-        <f>IF(A416&lt;&gt;"", A416 &amp; " - " &amp; B416, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="417">
-      <c r="C417">
-        <f>IF(A417&lt;&gt;"", A417 &amp; " - " &amp; B417, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="418">
-      <c r="C418">
-        <f>IF(A418&lt;&gt;"", A418 &amp; " - " &amp; B418, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="419">
-      <c r="C419">
-        <f>IF(A419&lt;&gt;"", A419 &amp; " - " &amp; B419, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="420">
-      <c r="C420">
-        <f>IF(A420&lt;&gt;"", A420 &amp; " - " &amp; B420, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="421">
-      <c r="C421">
-        <f>IF(A421&lt;&gt;"", A421 &amp; " - " &amp; B421, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="422">
-      <c r="C422">
-        <f>IF(A422&lt;&gt;"", A422 &amp; " - " &amp; B422, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="423">
-      <c r="C423">
-        <f>IF(A423&lt;&gt;"", A423 &amp; " - " &amp; B423, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="424">
-      <c r="C424">
-        <f>IF(A424&lt;&gt;"", A424 &amp; " - " &amp; B424, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="425">
-      <c r="C425">
-        <f>IF(A425&lt;&gt;"", A425 &amp; " - " &amp; B425, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="426">
-      <c r="C426">
-        <f>IF(A426&lt;&gt;"", A426 &amp; " - " &amp; B426, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="427">
-      <c r="C427">
-        <f>IF(A427&lt;&gt;"", A427 &amp; " - " &amp; B427, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="428">
-      <c r="C428">
-        <f>IF(A428&lt;&gt;"", A428 &amp; " - " &amp; B428, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="429">
-      <c r="C429">
-        <f>IF(A429&lt;&gt;"", A429 &amp; " - " &amp; B429, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="430">
-      <c r="C430">
-        <f>IF(A430&lt;&gt;"", A430 &amp; " - " &amp; B430, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="431">
-      <c r="C431">
-        <f>IF(A431&lt;&gt;"", A431 &amp; " - " &amp; B431, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="432">
-      <c r="C432">
-        <f>IF(A432&lt;&gt;"", A432 &amp; " - " &amp; B432, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="433">
-      <c r="C433">
-        <f>IF(A433&lt;&gt;"", A433 &amp; " - " &amp; B433, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="434">
-      <c r="C434">
-        <f>IF(A434&lt;&gt;"", A434 &amp; " - " &amp; B434, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="435">
-      <c r="C435">
-        <f>IF(A435&lt;&gt;"", A435 &amp; " - " &amp; B435, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="436">
-      <c r="C436">
-        <f>IF(A436&lt;&gt;"", A436 &amp; " - " &amp; B436, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="437">
-      <c r="C437">
-        <f>IF(A437&lt;&gt;"", A437 &amp; " - " &amp; B437, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="438">
-      <c r="C438">
-        <f>IF(A438&lt;&gt;"", A438 &amp; " - " &amp; B438, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="439">
-      <c r="C439">
-        <f>IF(A439&lt;&gt;"", A439 &amp; " - " &amp; B439, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="440">
-      <c r="C440">
-        <f>IF(A440&lt;&gt;"", A440 &amp; " - " &amp; B440, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="441">
-      <c r="C441">
-        <f>IF(A441&lt;&gt;"", A441 &amp; " - " &amp; B441, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="442">
-      <c r="C442">
-        <f>IF(A442&lt;&gt;"", A442 &amp; " - " &amp; B442, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="443">
-      <c r="C443">
-        <f>IF(A443&lt;&gt;"", A443 &amp; " - " &amp; B443, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444">
-      <c r="C444">
-        <f>IF(A444&lt;&gt;"", A444 &amp; " - " &amp; B444, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="445">
-      <c r="C445">
-        <f>IF(A445&lt;&gt;"", A445 &amp; " - " &amp; B445, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="446">
-      <c r="C446">
-        <f>IF(A446&lt;&gt;"", A446 &amp; " - " &amp; B446, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="447">
-      <c r="C447">
-        <f>IF(A447&lt;&gt;"", A447 &amp; " - " &amp; B447, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="448">
-      <c r="C448">
-        <f>IF(A448&lt;&gt;"", A448 &amp; " - " &amp; B448, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="449">
-      <c r="C449">
-        <f>IF(A449&lt;&gt;"", A449 &amp; " - " &amp; B449, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="450">
-      <c r="C450">
-        <f>IF(A450&lt;&gt;"", A450 &amp; " - " &amp; B450, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="451">
-      <c r="C451">
-        <f>IF(A451&lt;&gt;"", A451 &amp; " - " &amp; B451, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452">
-      <c r="C452">
-        <f>IF(A452&lt;&gt;"", A452 &amp; " - " &amp; B452, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453">
-      <c r="C453">
-        <f>IF(A453&lt;&gt;"", A453 &amp; " - " &amp; B453, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="454">
-      <c r="C454">
-        <f>IF(A454&lt;&gt;"", A454 &amp; " - " &amp; B454, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="455">
-      <c r="C455">
-        <f>IF(A455&lt;&gt;"", A455 &amp; " - " &amp; B455, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="456">
-      <c r="C456">
-        <f>IF(A456&lt;&gt;"", A456 &amp; " - " &amp; B456, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="457">
-      <c r="C457">
-        <f>IF(A457&lt;&gt;"", A457 &amp; " - " &amp; B457, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="458">
-      <c r="C458">
-        <f>IF(A458&lt;&gt;"", A458 &amp; " - " &amp; B458, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="459">
-      <c r="C459">
-        <f>IF(A459&lt;&gt;"", A459 &amp; " - " &amp; B459, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="460">
-      <c r="C460">
-        <f>IF(A460&lt;&gt;"", A460 &amp; " - " &amp; B460, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="461">
-      <c r="C461">
-        <f>IF(A461&lt;&gt;"", A461 &amp; " - " &amp; B461, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="462">
-      <c r="C462">
-        <f>IF(A462&lt;&gt;"", A462 &amp; " - " &amp; B462, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="463">
-      <c r="C463">
-        <f>IF(A463&lt;&gt;"", A463 &amp; " - " &amp; B463, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="464">
-      <c r="C464">
-        <f>IF(A464&lt;&gt;"", A464 &amp; " - " &amp; B464, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="465">
-      <c r="C465">
-        <f>IF(A465&lt;&gt;"", A465 &amp; " - " &amp; B465, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="466">
-      <c r="C466">
-        <f>IF(A466&lt;&gt;"", A466 &amp; " - " &amp; B466, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="467">
-      <c r="C467">
-        <f>IF(A467&lt;&gt;"", A467 &amp; " - " &amp; B467, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="468">
-      <c r="C468">
-        <f>IF(A468&lt;&gt;"", A468 &amp; " - " &amp; B468, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="469">
-      <c r="C469">
-        <f>IF(A469&lt;&gt;"", A469 &amp; " - " &amp; B469, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="470">
-      <c r="C470">
-        <f>IF(A470&lt;&gt;"", A470 &amp; " - " &amp; B470, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="471">
-      <c r="C471">
-        <f>IF(A471&lt;&gt;"", A471 &amp; " - " &amp; B471, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="472">
-      <c r="C472">
-        <f>IF(A472&lt;&gt;"", A472 &amp; " - " &amp; B472, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="473">
-      <c r="C473">
-        <f>IF(A473&lt;&gt;"", A473 &amp; " - " &amp; B473, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="474">
-      <c r="C474">
-        <f>IF(A474&lt;&gt;"", A474 &amp; " - " &amp; B474, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="475">
-      <c r="C475">
-        <f>IF(A475&lt;&gt;"", A475 &amp; " - " &amp; B475, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="476">
-      <c r="C476">
-        <f>IF(A476&lt;&gt;"", A476 &amp; " - " &amp; B476, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="477">
-      <c r="C477">
-        <f>IF(A477&lt;&gt;"", A477 &amp; " - " &amp; B477, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="478">
-      <c r="C478">
-        <f>IF(A478&lt;&gt;"", A478 &amp; " - " &amp; B478, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="479">
-      <c r="C479">
-        <f>IF(A479&lt;&gt;"", A479 &amp; " - " &amp; B479, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="480">
-      <c r="C480">
-        <f>IF(A480&lt;&gt;"", A480 &amp; " - " &amp; B480, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="481">
-      <c r="C481">
-        <f>IF(A481&lt;&gt;"", A481 &amp; " - " &amp; B481, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="482">
-      <c r="C482">
-        <f>IF(A482&lt;&gt;"", A482 &amp; " - " &amp; B482, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="483">
-      <c r="C483">
-        <f>IF(A483&lt;&gt;"", A483 &amp; " - " &amp; B483, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="484">
-      <c r="C484">
-        <f>IF(A484&lt;&gt;"", A484 &amp; " - " &amp; B484, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="485">
-      <c r="C485">
-        <f>IF(A485&lt;&gt;"", A485 &amp; " - " &amp; B485, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="486">
-      <c r="C486">
-        <f>IF(A486&lt;&gt;"", A486 &amp; " - " &amp; B486, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="487">
-      <c r="C487">
-        <f>IF(A487&lt;&gt;"", A487 &amp; " - " &amp; B487, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="488">
-      <c r="C488">
-        <f>IF(A488&lt;&gt;"", A488 &amp; " - " &amp; B488, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="489">
-      <c r="C489">
-        <f>IF(A489&lt;&gt;"", A489 &amp; " - " &amp; B489, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="490">
-      <c r="C490">
-        <f>IF(A490&lt;&gt;"", A490 &amp; " - " &amp; B490, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="491">
-      <c r="C491">
-        <f>IF(A491&lt;&gt;"", A491 &amp; " - " &amp; B491, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="492">
-      <c r="C492">
-        <f>IF(A492&lt;&gt;"", A492 &amp; " - " &amp; B492, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="493">
-      <c r="C493">
-        <f>IF(A493&lt;&gt;"", A493 &amp; " - " &amp; B493, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="494">
-      <c r="C494">
-        <f>IF(A494&lt;&gt;"", A494 &amp; " - " &amp; B494, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="495">
-      <c r="C495">
-        <f>IF(A495&lt;&gt;"", A495 &amp; " - " &amp; B495, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="496">
-      <c r="C496">
-        <f>IF(A496&lt;&gt;"", A496 &amp; " - " &amp; B496, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="497">
-      <c r="C497">
-        <f>IF(A497&lt;&gt;"", A497 &amp; " - " &amp; B497, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="498">
-      <c r="C498">
-        <f>IF(A498&lt;&gt;"", A498 &amp; " - " &amp; B498, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="499">
-      <c r="C499">
-        <f>IF(A499&lt;&gt;"", A499 &amp; " - " &amp; B499, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="500">
-      <c r="C500">
-        <f>IF(A500&lt;&gt;"", A500 &amp; " - " &amp; B500, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="501">
-      <c r="C501">
-        <f>IF(A501&lt;&gt;"", A501 &amp; " - " &amp; B501, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="502">
-      <c r="C502">
-        <f>IF(A502&lt;&gt;"", A502 &amp; " - " &amp; B502, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="503">
-      <c r="C503">
-        <f>IF(A503&lt;&gt;"", A503 &amp; " - " &amp; B503, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="504">
-      <c r="C504">
-        <f>IF(A504&lt;&gt;"", A504 &amp; " - " &amp; B504, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="505">
-      <c r="C505">
-        <f>IF(A505&lt;&gt;"", A505 &amp; " - " &amp; B505, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="506">
-      <c r="C506">
-        <f>IF(A506&lt;&gt;"", A506 &amp; " - " &amp; B506, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="507">
-      <c r="C507">
-        <f>IF(A507&lt;&gt;"", A507 &amp; " - " &amp; B507, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="508">
-      <c r="C508">
-        <f>IF(A508&lt;&gt;"", A508 &amp; " - " &amp; B508, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="509">
-      <c r="C509">
-        <f>IF(A509&lt;&gt;"", A509 &amp; " - " &amp; B509, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="510">
-      <c r="C510">
-        <f>IF(A510&lt;&gt;"", A510 &amp; " - " &amp; B510, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="511">
-      <c r="C511">
-        <f>IF(A511&lt;&gt;"", A511 &amp; " - " &amp; B511, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="512">
-      <c r="C512">
-        <f>IF(A512&lt;&gt;"", A512 &amp; " - " &amp; B512, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="513">
-      <c r="C513">
-        <f>IF(A513&lt;&gt;"", A513 &amp; " - " &amp; B513, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="514">
-      <c r="C514">
-        <f>IF(A514&lt;&gt;"", A514 &amp; " - " &amp; B514, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="515">
-      <c r="C515">
-        <f>IF(A515&lt;&gt;"", A515 &amp; " - " &amp; B515, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="516">
-      <c r="C516">
-        <f>IF(A516&lt;&gt;"", A516 &amp; " - " &amp; B516, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="517">
-      <c r="C517">
-        <f>IF(A517&lt;&gt;"", A517 &amp; " - " &amp; B517, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="518">
-      <c r="C518">
-        <f>IF(A518&lt;&gt;"", A518 &amp; " - " &amp; B518, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="519">
-      <c r="C519">
-        <f>IF(A519&lt;&gt;"", A519 &amp; " - " &amp; B519, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="520">
-      <c r="C520">
-        <f>IF(A520&lt;&gt;"", A520 &amp; " - " &amp; B520, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="521">
-      <c r="C521">
-        <f>IF(A521&lt;&gt;"", A521 &amp; " - " &amp; B521, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="522">
-      <c r="C522">
-        <f>IF(A522&lt;&gt;"", A522 &amp; " - " &amp; B522, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="523">
-      <c r="C523">
-        <f>IF(A523&lt;&gt;"", A523 &amp; " - " &amp; B523, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="524">
-      <c r="C524">
-        <f>IF(A524&lt;&gt;"", A524 &amp; " - " &amp; B524, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="525">
-      <c r="C525">
-        <f>IF(A525&lt;&gt;"", A525 &amp; " - " &amp; B525, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="526">
-      <c r="C526">
-        <f>IF(A526&lt;&gt;"", A526 &amp; " - " &amp; B526, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="527">
-      <c r="C527">
-        <f>IF(A527&lt;&gt;"", A527 &amp; " - " &amp; B527, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="528">
-      <c r="C528">
-        <f>IF(A528&lt;&gt;"", A528 &amp; " - " &amp; B528, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="529">
-      <c r="C529">
-        <f>IF(A529&lt;&gt;"", A529 &amp; " - " &amp; B529, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="530">
-      <c r="C530">
-        <f>IF(A530&lt;&gt;"", A530 &amp; " - " &amp; B530, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="531">
-      <c r="C531">
-        <f>IF(A531&lt;&gt;"", A531 &amp; " - " &amp; B531, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="532">
-      <c r="C532">
-        <f>IF(A532&lt;&gt;"", A532 &amp; " - " &amp; B532, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="533">
-      <c r="C533">
-        <f>IF(A533&lt;&gt;"", A533 &amp; " - " &amp; B533, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="534">
-      <c r="C534">
-        <f>IF(A534&lt;&gt;"", A534 &amp; " - " &amp; B534, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="535">
-      <c r="C535">
-        <f>IF(A535&lt;&gt;"", A535 &amp; " - " &amp; B535, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="536">
-      <c r="C536">
-        <f>IF(A536&lt;&gt;"", A536 &amp; " - " &amp; B536, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="537">
-      <c r="C537">
-        <f>IF(A537&lt;&gt;"", A537 &amp; " - " &amp; B537, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="538">
-      <c r="C538">
-        <f>IF(A538&lt;&gt;"", A538 &amp; " - " &amp; B538, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="539">
-      <c r="C539">
-        <f>IF(A539&lt;&gt;"", A539 &amp; " - " &amp; B539, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="540">
-      <c r="C540">
-        <f>IF(A540&lt;&gt;"", A540 &amp; " - " &amp; B540, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="541">
-      <c r="C541">
-        <f>IF(A541&lt;&gt;"", A541 &amp; " - " &amp; B541, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="542">
-      <c r="C542">
-        <f>IF(A542&lt;&gt;"", A542 &amp; " - " &amp; B542, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="543">
-      <c r="C543">
-        <f>IF(A543&lt;&gt;"", A543 &amp; " - " &amp; B543, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="544">
-      <c r="C544">
-        <f>IF(A544&lt;&gt;"", A544 &amp; " - " &amp; B544, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="545">
-      <c r="C545">
-        <f>IF(A545&lt;&gt;"", A545 &amp; " - " &amp; B545, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="546">
-      <c r="C546">
-        <f>IF(A546&lt;&gt;"", A546 &amp; " - " &amp; B546, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="547">
-      <c r="C547">
-        <f>IF(A547&lt;&gt;"", A547 &amp; " - " &amp; B547, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="548">
-      <c r="C548">
-        <f>IF(A548&lt;&gt;"", A548 &amp; " - " &amp; B548, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="549">
-      <c r="C549">
-        <f>IF(A549&lt;&gt;"", A549 &amp; " - " &amp; B549, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="550">
-      <c r="C550">
-        <f>IF(A550&lt;&gt;"", A550 &amp; " - " &amp; B550, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="551">
-      <c r="C551">
-        <f>IF(A551&lt;&gt;"", A551 &amp; " - " &amp; B551, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="552">
-      <c r="C552">
-        <f>IF(A552&lt;&gt;"", A552 &amp; " - " &amp; B552, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="553">
-      <c r="C553">
-        <f>IF(A553&lt;&gt;"", A553 &amp; " - " &amp; B553, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="554">
-      <c r="C554">
-        <f>IF(A554&lt;&gt;"", A554 &amp; " - " &amp; B554, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="555">
-      <c r="C555">
-        <f>IF(A555&lt;&gt;"", A555 &amp; " - " &amp; B555, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="556">
-      <c r="C556">
-        <f>IF(A556&lt;&gt;"", A556 &amp; " - " &amp; B556, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="557">
-      <c r="C557">
-        <f>IF(A557&lt;&gt;"", A557 &amp; " - " &amp; B557, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="558">
-      <c r="C558">
-        <f>IF(A558&lt;&gt;"", A558 &amp; " - " &amp; B558, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="559">
-      <c r="C559">
-        <f>IF(A559&lt;&gt;"", A559 &amp; " - " &amp; B559, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="560">
-      <c r="C560">
-        <f>IF(A560&lt;&gt;"", A560 &amp; " - " &amp; B560, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="561">
-      <c r="C561">
-        <f>IF(A561&lt;&gt;"", A561 &amp; " - " &amp; B561, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="562">
-      <c r="C562">
-        <f>IF(A562&lt;&gt;"", A562 &amp; " - " &amp; B562, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="563">
-      <c r="C563">
-        <f>IF(A563&lt;&gt;"", A563 &amp; " - " &amp; B563, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="564">
-      <c r="C564">
-        <f>IF(A564&lt;&gt;"", A564 &amp; " - " &amp; B564, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="565">
-      <c r="C565">
-        <f>IF(A565&lt;&gt;"", A565 &amp; " - " &amp; B565, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="566">
-      <c r="C566">
-        <f>IF(A566&lt;&gt;"", A566 &amp; " - " &amp; B566, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="567">
-      <c r="C567">
-        <f>IF(A567&lt;&gt;"", A567 &amp; " - " &amp; B567, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="568">
-      <c r="C568">
-        <f>IF(A568&lt;&gt;"", A568 &amp; " - " &amp; B568, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="569">
-      <c r="C569">
-        <f>IF(A569&lt;&gt;"", A569 &amp; " - " &amp; B569, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="570">
-      <c r="C570">
-        <f>IF(A570&lt;&gt;"", A570 &amp; " - " &amp; B570, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="571">
-      <c r="C571">
-        <f>IF(A571&lt;&gt;"", A571 &amp; " - " &amp; B571, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="572">
-      <c r="C572">
-        <f>IF(A572&lt;&gt;"", A572 &amp; " - " &amp; B572, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="573">
-      <c r="C573">
-        <f>IF(A573&lt;&gt;"", A573 &amp; " - " &amp; B573, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="574">
-      <c r="C574">
-        <f>IF(A574&lt;&gt;"", A574 &amp; " - " &amp; B574, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="575">
-      <c r="C575">
-        <f>IF(A575&lt;&gt;"", A575 &amp; " - " &amp; B575, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="576">
-      <c r="C576">
-        <f>IF(A576&lt;&gt;"", A576 &amp; " - " &amp; B576, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="577">
-      <c r="C577">
-        <f>IF(A577&lt;&gt;"", A577 &amp; " - " &amp; B577, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="578">
-      <c r="C578">
-        <f>IF(A578&lt;&gt;"", A578 &amp; " - " &amp; B578, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="579">
-      <c r="C579">
-        <f>IF(A579&lt;&gt;"", A579 &amp; " - " &amp; B579, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="580">
-      <c r="C580">
-        <f>IF(A580&lt;&gt;"", A580 &amp; " - " &amp; B580, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="581">
-      <c r="C581">
-        <f>IF(A581&lt;&gt;"", A581 &amp; " - " &amp; B581, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="582">
-      <c r="C582">
-        <f>IF(A582&lt;&gt;"", A582 &amp; " - " &amp; B582, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="583">
-      <c r="C583">
-        <f>IF(A583&lt;&gt;"", A583 &amp; " - " &amp; B583, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="584">
-      <c r="C584">
-        <f>IF(A584&lt;&gt;"", A584 &amp; " - " &amp; B584, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="585">
-      <c r="C585">
-        <f>IF(A585&lt;&gt;"", A585 &amp; " - " &amp; B585, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="586">
-      <c r="C586">
-        <f>IF(A586&lt;&gt;"", A586 &amp; " - " &amp; B586, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="587">
-      <c r="C587">
-        <f>IF(A587&lt;&gt;"", A587 &amp; " - " &amp; B587, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="588">
-      <c r="C588">
-        <f>IF(A588&lt;&gt;"", A588 &amp; " - " &amp; B588, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="589">
-      <c r="C589">
-        <f>IF(A589&lt;&gt;"", A589 &amp; " - " &amp; B589, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="590">
-      <c r="C590">
-        <f>IF(A590&lt;&gt;"", A590 &amp; " - " &amp; B590, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="591">
-      <c r="C591">
-        <f>IF(A591&lt;&gt;"", A591 &amp; " - " &amp; B591, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="592">
-      <c r="C592">
-        <f>IF(A592&lt;&gt;"", A592 &amp; " - " &amp; B592, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="593">
-      <c r="C593">
-        <f>IF(A593&lt;&gt;"", A593 &amp; " - " &amp; B593, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="594">
-      <c r="C594">
-        <f>IF(A594&lt;&gt;"", A594 &amp; " - " &amp; B594, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="595">
-      <c r="C595">
-        <f>IF(A595&lt;&gt;"", A595 &amp; " - " &amp; B595, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="596">
-      <c r="C596">
-        <f>IF(A596&lt;&gt;"", A596 &amp; " - " &amp; B596, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="597">
-      <c r="C597">
-        <f>IF(A597&lt;&gt;"", A597 &amp; " - " &amp; B597, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="598">
-      <c r="C598">
-        <f>IF(A598&lt;&gt;"", A598 &amp; " - " &amp; B598, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="599">
-      <c r="C599">
-        <f>IF(A599&lt;&gt;"", A599 &amp; " - " &amp; B599, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="600">
-      <c r="C600">
-        <f>IF(A600&lt;&gt;"", A600 &amp; " - " &amp; B600, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="601">
-      <c r="C601">
-        <f>IF(A601&lt;&gt;"", A601 &amp; " - " &amp; B601, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="602">
-      <c r="C602">
-        <f>IF(A602&lt;&gt;"", A602 &amp; " - " &amp; B602, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="603">
-      <c r="C603">
-        <f>IF(A603&lt;&gt;"", A603 &amp; " - " &amp; B603, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="604">
-      <c r="C604">
-        <f>IF(A604&lt;&gt;"", A604 &amp; " - " &amp; B604, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="605">
-      <c r="C605">
-        <f>IF(A605&lt;&gt;"", A605 &amp; " - " &amp; B605, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="606">
-      <c r="C606">
-        <f>IF(A606&lt;&gt;"", A606 &amp; " - " &amp; B606, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="607">
-      <c r="C607">
-        <f>IF(A607&lt;&gt;"", A607 &amp; " - " &amp; B607, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="608">
-      <c r="C608">
-        <f>IF(A608&lt;&gt;"", A608 &amp; " - " &amp; B608, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="609">
-      <c r="C609">
-        <f>IF(A609&lt;&gt;"", A609 &amp; " - " &amp; B609, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="610">
-      <c r="C610">
-        <f>IF(A610&lt;&gt;"", A610 &amp; " - " &amp; B610, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="611">
-      <c r="C611">
-        <f>IF(A611&lt;&gt;"", A611 &amp; " - " &amp; B611, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="612">
-      <c r="C612">
-        <f>IF(A612&lt;&gt;"", A612 &amp; " - " &amp; B612, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="613">
-      <c r="C613">
-        <f>IF(A613&lt;&gt;"", A613 &amp; " - " &amp; B613, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="614">
-      <c r="C614">
-        <f>IF(A614&lt;&gt;"", A614 &amp; " - " &amp; B614, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="615">
-      <c r="C615">
-        <f>IF(A615&lt;&gt;"", A615 &amp; " - " &amp; B615, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="616">
-      <c r="C616">
-        <f>IF(A616&lt;&gt;"", A616 &amp; " - " &amp; B616, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="617">
-      <c r="C617">
-        <f>IF(A617&lt;&gt;"", A617 &amp; " - " &amp; B617, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="618">
-      <c r="C618">
-        <f>IF(A618&lt;&gt;"", A618 &amp; " - " &amp; B618, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="619">
-      <c r="C619">
-        <f>IF(A619&lt;&gt;"", A619 &amp; " - " &amp; B619, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="620">
-      <c r="C620">
-        <f>IF(A620&lt;&gt;"", A620 &amp; " - " &amp; B620, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="621">
-      <c r="C621">
-        <f>IF(A621&lt;&gt;"", A621 &amp; " - " &amp; B621, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="622">
-      <c r="C622">
-        <f>IF(A622&lt;&gt;"", A622 &amp; " - " &amp; B622, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="623">
-      <c r="C623">
-        <f>IF(A623&lt;&gt;"", A623 &amp; " - " &amp; B623, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="624">
-      <c r="C624">
-        <f>IF(A624&lt;&gt;"", A624 &amp; " - " &amp; B624, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="625">
-      <c r="C625">
-        <f>IF(A625&lt;&gt;"", A625 &amp; " - " &amp; B625, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="626">
-      <c r="C626">
-        <f>IF(A626&lt;&gt;"", A626 &amp; " - " &amp; B626, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="627">
-      <c r="C627">
-        <f>IF(A627&lt;&gt;"", A627 &amp; " - " &amp; B627, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="628">
-      <c r="C628">
-        <f>IF(A628&lt;&gt;"", A628 &amp; " - " &amp; B628, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="629">
-      <c r="C629">
-        <f>IF(A629&lt;&gt;"", A629 &amp; " - " &amp; B629, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="630">
-      <c r="C630">
-        <f>IF(A630&lt;&gt;"", A630 &amp; " - " &amp; B630, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="631">
-      <c r="C631">
-        <f>IF(A631&lt;&gt;"", A631 &amp; " - " &amp; B631, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="632">
-      <c r="C632">
-        <f>IF(A632&lt;&gt;"", A632 &amp; " - " &amp; B632, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="633">
-      <c r="C633">
-        <f>IF(A633&lt;&gt;"", A633 &amp; " - " &amp; B633, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="634">
-      <c r="C634">
-        <f>IF(A634&lt;&gt;"", A634 &amp; " - " &amp; B634, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="635">
-      <c r="C635">
-        <f>IF(A635&lt;&gt;"", A635 &amp; " - " &amp; B635, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="636">
-      <c r="C636">
-        <f>IF(A636&lt;&gt;"", A636 &amp; " - " &amp; B636, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="637">
-      <c r="C637">
-        <f>IF(A637&lt;&gt;"", A637 &amp; " - " &amp; B637, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="638">
-      <c r="C638">
-        <f>IF(A638&lt;&gt;"", A638 &amp; " - " &amp; B638, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="639">
-      <c r="C639">
-        <f>IF(A639&lt;&gt;"", A639 &amp; " - " &amp; B639, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="640">
-      <c r="C640">
-        <f>IF(A640&lt;&gt;"", A640 &amp; " - " &amp; B640, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="641">
-      <c r="C641">
-        <f>IF(A641&lt;&gt;"", A641 &amp; " - " &amp; B641, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="642">
-      <c r="C642">
-        <f>IF(A642&lt;&gt;"", A642 &amp; " - " &amp; B642, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="643">
-      <c r="C643">
-        <f>IF(A643&lt;&gt;"", A643 &amp; " - " &amp; B643, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="644">
-      <c r="C644">
-        <f>IF(A644&lt;&gt;"", A644 &amp; " - " &amp; B644, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="645">
-      <c r="C645">
-        <f>IF(A645&lt;&gt;"", A645 &amp; " - " &amp; B645, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="646">
-      <c r="C646">
-        <f>IF(A646&lt;&gt;"", A646 &amp; " - " &amp; B646, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="647">
-      <c r="C647">
-        <f>IF(A647&lt;&gt;"", A647 &amp; " - " &amp; B647, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="648">
-      <c r="C648">
-        <f>IF(A648&lt;&gt;"", A648 &amp; " - " &amp; B648, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="649">
-      <c r="C649">
-        <f>IF(A649&lt;&gt;"", A649 &amp; " - " &amp; B649, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="650">
-      <c r="C650">
-        <f>IF(A650&lt;&gt;"", A650 &amp; " - " &amp; B650, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="651">
-      <c r="C651">
-        <f>IF(A651&lt;&gt;"", A651 &amp; " - " &amp; B651, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="652">
-      <c r="C652">
-        <f>IF(A652&lt;&gt;"", A652 &amp; " - " &amp; B652, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="653">
-      <c r="C653">
-        <f>IF(A653&lt;&gt;"", A653 &amp; " - " &amp; B653, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="654">
-      <c r="C654">
-        <f>IF(A654&lt;&gt;"", A654 &amp; " - " &amp; B654, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="655">
-      <c r="C655">
-        <f>IF(A655&lt;&gt;"", A655 &amp; " - " &amp; B655, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="656">
-      <c r="C656">
-        <f>IF(A656&lt;&gt;"", A656 &amp; " - " &amp; B656, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="657">
-      <c r="C657">
-        <f>IF(A657&lt;&gt;"", A657 &amp; " - " &amp; B657, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="658">
-      <c r="C658">
-        <f>IF(A658&lt;&gt;"", A658 &amp; " - " &amp; B658, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="659">
-      <c r="C659">
-        <f>IF(A659&lt;&gt;"", A659 &amp; " - " &amp; B659, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="660">
-      <c r="C660">
-        <f>IF(A660&lt;&gt;"", A660 &amp; " - " &amp; B660, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="661">
-      <c r="C661">
-        <f>IF(A661&lt;&gt;"", A661 &amp; " - " &amp; B661, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="662">
-      <c r="C662">
-        <f>IF(A662&lt;&gt;"", A662 &amp; " - " &amp; B662, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="663">
-      <c r="C663">
-        <f>IF(A663&lt;&gt;"", A663 &amp; " - " &amp; B663, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="664">
-      <c r="C664">
-        <f>IF(A664&lt;&gt;"", A664 &amp; " - " &amp; B664, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="665">
-      <c r="C665">
-        <f>IF(A665&lt;&gt;"", A665 &amp; " - " &amp; B665, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="666">
-      <c r="C666">
-        <f>IF(A666&lt;&gt;"", A666 &amp; " - " &amp; B666, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="667">
-      <c r="C667">
-        <f>IF(A667&lt;&gt;"", A667 &amp; " - " &amp; B667, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="668">
-      <c r="C668">
-        <f>IF(A668&lt;&gt;"", A668 &amp; " - " &amp; B668, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="669">
-      <c r="C669">
-        <f>IF(A669&lt;&gt;"", A669 &amp; " - " &amp; B669, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="670">
-      <c r="C670">
-        <f>IF(A670&lt;&gt;"", A670 &amp; " - " &amp; B670, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="671">
-      <c r="C671">
-        <f>IF(A671&lt;&gt;"", A671 &amp; " - " &amp; B671, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="672">
-      <c r="C672">
-        <f>IF(A672&lt;&gt;"", A672 &amp; " - " &amp; B672, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="673">
-      <c r="C673">
-        <f>IF(A673&lt;&gt;"", A673 &amp; " - " &amp; B673, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="674">
-      <c r="C674">
-        <f>IF(A674&lt;&gt;"", A674 &amp; " - " &amp; B674, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="675">
-      <c r="C675">
-        <f>IF(A675&lt;&gt;"", A675 &amp; " - " &amp; B675, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="676">
-      <c r="C676">
-        <f>IF(A676&lt;&gt;"", A676 &amp; " - " &amp; B676, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="677">
-      <c r="C677">
-        <f>IF(A677&lt;&gt;"", A677 &amp; " - " &amp; B677, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="678">
-      <c r="C678">
-        <f>IF(A678&lt;&gt;"", A678 &amp; " - " &amp; B678, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="679">
-      <c r="C679">
-        <f>IF(A679&lt;&gt;"", A679 &amp; " - " &amp; B679, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="680">
-      <c r="C680">
-        <f>IF(A680&lt;&gt;"", A680 &amp; " - " &amp; B680, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="681">
-      <c r="C681">
-        <f>IF(A681&lt;&gt;"", A681 &amp; " - " &amp; B681, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="682">
-      <c r="C682">
-        <f>IF(A682&lt;&gt;"", A682 &amp; " - " &amp; B682, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="683">
-      <c r="C683">
-        <f>IF(A683&lt;&gt;"", A683 &amp; " - " &amp; B683, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="684">
-      <c r="C684">
-        <f>IF(A684&lt;&gt;"", A684 &amp; " - " &amp; B684, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="685">
-      <c r="C685">
-        <f>IF(A685&lt;&gt;"", A685 &amp; " - " &amp; B685, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="686">
-      <c r="C686">
-        <f>IF(A686&lt;&gt;"", A686 &amp; " - " &amp; B686, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="687">
-      <c r="C687">
-        <f>IF(A687&lt;&gt;"", A687 &amp; " - " &amp; B687, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="688">
-      <c r="C688">
-        <f>IF(A688&lt;&gt;"", A688 &amp; " - " &amp; B688, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="689">
-      <c r="C689">
-        <f>IF(A689&lt;&gt;"", A689 &amp; " - " &amp; B689, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="690">
-      <c r="C690">
-        <f>IF(A690&lt;&gt;"", A690 &amp; " - " &amp; B690, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="691">
-      <c r="C691">
-        <f>IF(A691&lt;&gt;"", A691 &amp; " - " &amp; B691, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="692">
-      <c r="C692">
-        <f>IF(A692&lt;&gt;"", A692 &amp; " - " &amp; B692, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="693">
-      <c r="C693">
-        <f>IF(A693&lt;&gt;"", A693 &amp; " - " &amp; B693, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="694">
-      <c r="C694">
-        <f>IF(A694&lt;&gt;"", A694 &amp; " - " &amp; B694, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="695">
-      <c r="C695">
-        <f>IF(A695&lt;&gt;"", A695 &amp; " - " &amp; B695, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="696">
-      <c r="C696">
-        <f>IF(A696&lt;&gt;"", A696 &amp; " - " &amp; B696, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="697">
-      <c r="C697">
-        <f>IF(A697&lt;&gt;"", A697 &amp; " - " &amp; B697, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="698">
-      <c r="C698">
-        <f>IF(A698&lt;&gt;"", A698 &amp; " - " &amp; B698, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="699">
-      <c r="C699">
-        <f>IF(A699&lt;&gt;"", A699 &amp; " - " &amp; B699, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="700">
-      <c r="C700">
-        <f>IF(A700&lt;&gt;"", A700 &amp; " - " &amp; B700, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="701">
-      <c r="C701">
-        <f>IF(A701&lt;&gt;"", A701 &amp; " - " &amp; B701, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="702">
-      <c r="C702">
-        <f>IF(A702&lt;&gt;"", A702 &amp; " - " &amp; B702, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="703">
-      <c r="C703">
-        <f>IF(A703&lt;&gt;"", A703 &amp; " - " &amp; B703, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="704">
-      <c r="C704">
-        <f>IF(A704&lt;&gt;"", A704 &amp; " - " &amp; B704, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="705">
-      <c r="C705">
-        <f>IF(A705&lt;&gt;"", A705 &amp; " - " &amp; B705, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="706">
-      <c r="C706">
-        <f>IF(A706&lt;&gt;"", A706 &amp; " - " &amp; B706, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="707">
-      <c r="C707">
-        <f>IF(A707&lt;&gt;"", A707 &amp; " - " &amp; B707, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="708">
-      <c r="C708">
-        <f>IF(A708&lt;&gt;"", A708 &amp; " - " &amp; B708, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="709">
-      <c r="C709">
-        <f>IF(A709&lt;&gt;"", A709 &amp; " - " &amp; B709, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="710">
-      <c r="C710">
-        <f>IF(A710&lt;&gt;"", A710 &amp; " - " &amp; B710, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="711">
-      <c r="C711">
-        <f>IF(A711&lt;&gt;"", A711 &amp; " - " &amp; B711, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="712">
-      <c r="C712">
-        <f>IF(A712&lt;&gt;"", A712 &amp; " - " &amp; B712, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="713">
-      <c r="C713">
-        <f>IF(A713&lt;&gt;"", A713 &amp; " - " &amp; B713, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="714">
-      <c r="C714">
-        <f>IF(A714&lt;&gt;"", A714 &amp; " - " &amp; B714, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="715">
-      <c r="C715">
-        <f>IF(A715&lt;&gt;"", A715 &amp; " - " &amp; B715, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="716">
-      <c r="C716">
-        <f>IF(A716&lt;&gt;"", A716 &amp; " - " &amp; B716, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="717">
-      <c r="C717">
-        <f>IF(A717&lt;&gt;"", A717 &amp; " - " &amp; B717, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="718">
-      <c r="C718">
-        <f>IF(A718&lt;&gt;"", A718 &amp; " - " &amp; B718, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="719">
-      <c r="C719">
-        <f>IF(A719&lt;&gt;"", A719 &amp; " - " &amp; B719, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="720">
-      <c r="C720">
-        <f>IF(A720&lt;&gt;"", A720 &amp; " - " &amp; B720, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="721">
-      <c r="C721">
-        <f>IF(A721&lt;&gt;"", A721 &amp; " - " &amp; B721, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="722">
-      <c r="C722">
-        <f>IF(A722&lt;&gt;"", A722 &amp; " - " &amp; B722, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="723">
-      <c r="C723">
-        <f>IF(A723&lt;&gt;"", A723 &amp; " - " &amp; B723, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="724">
-      <c r="C724">
-        <f>IF(A724&lt;&gt;"", A724 &amp; " - " &amp; B724, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="725">
-      <c r="C725">
-        <f>IF(A725&lt;&gt;"", A725 &amp; " - " &amp; B725, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="726">
-      <c r="C726">
-        <f>IF(A726&lt;&gt;"", A726 &amp; " - " &amp; B726, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="727">
-      <c r="C727">
-        <f>IF(A727&lt;&gt;"", A727 &amp; " - " &amp; B727, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="728">
-      <c r="C728">
-        <f>IF(A728&lt;&gt;"", A728 &amp; " - " &amp; B728, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="729">
-      <c r="C729">
-        <f>IF(A729&lt;&gt;"", A729 &amp; " - " &amp; B729, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="730">
-      <c r="C730">
-        <f>IF(A730&lt;&gt;"", A730 &amp; " - " &amp; B730, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="731">
-      <c r="C731">
-        <f>IF(A731&lt;&gt;"", A731 &amp; " - " &amp; B731, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="732">
-      <c r="C732">
-        <f>IF(A732&lt;&gt;"", A732 &amp; " - " &amp; B732, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="733">
-      <c r="C733">
-        <f>IF(A733&lt;&gt;"", A733 &amp; " - " &amp; B733, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="734">
-      <c r="C734">
-        <f>IF(A734&lt;&gt;"", A734 &amp; " - " &amp; B734, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="735">
-      <c r="C735">
-        <f>IF(A735&lt;&gt;"", A735 &amp; " - " &amp; B735, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="736">
-      <c r="C736">
-        <f>IF(A736&lt;&gt;"", A736 &amp; " - " &amp; B736, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="737">
-      <c r="C737">
-        <f>IF(A737&lt;&gt;"", A737 &amp; " - " &amp; B737, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="738">
-      <c r="C738">
-        <f>IF(A738&lt;&gt;"", A738 &amp; " - " &amp; B738, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="739">
-      <c r="C739">
-        <f>IF(A739&lt;&gt;"", A739 &amp; " - " &amp; B739, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="740">
-      <c r="C740">
-        <f>IF(A740&lt;&gt;"", A740 &amp; " - " &amp; B740, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="741">
-      <c r="C741">
-        <f>IF(A741&lt;&gt;"", A741 &amp; " - " &amp; B741, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="742">
-      <c r="C742">
-        <f>IF(A742&lt;&gt;"", A742 &amp; " - " &amp; B742, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="743">
-      <c r="C743">
-        <f>IF(A743&lt;&gt;"", A743 &amp; " - " &amp; B743, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="744">
-      <c r="C744">
-        <f>IF(A744&lt;&gt;"", A744 &amp; " - " &amp; B744, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="745">
-      <c r="C745">
-        <f>IF(A745&lt;&gt;"", A745 &amp; " - " &amp; B745, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="746">
-      <c r="C746">
-        <f>IF(A746&lt;&gt;"", A746 &amp; " - " &amp; B746, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="747">
-      <c r="C747">
-        <f>IF(A747&lt;&gt;"", A747 &amp; " - " &amp; B747, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="748">
-      <c r="C748">
-        <f>IF(A748&lt;&gt;"", A748 &amp; " - " &amp; B748, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="749">
-      <c r="C749">
-        <f>IF(A749&lt;&gt;"", A749 &amp; " - " &amp; B749, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="750">
-      <c r="C750">
-        <f>IF(A750&lt;&gt;"", A750 &amp; " - " &amp; B750, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="751">
-      <c r="C751">
-        <f>IF(A751&lt;&gt;"", A751 &amp; " - " &amp; B751, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="752">
-      <c r="C752">
-        <f>IF(A752&lt;&gt;"", A752 &amp; " - " &amp; B752, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="753">
-      <c r="C753">
-        <f>IF(A753&lt;&gt;"", A753 &amp; " - " &amp; B753, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="754">
-      <c r="C754">
-        <f>IF(A754&lt;&gt;"", A754 &amp; " - " &amp; B754, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="755">
-      <c r="C755">
-        <f>IF(A755&lt;&gt;"", A755 &amp; " - " &amp; B755, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="756">
-      <c r="C756">
-        <f>IF(A756&lt;&gt;"", A756 &amp; " - " &amp; B756, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="757">
-      <c r="C757">
-        <f>IF(A757&lt;&gt;"", A757 &amp; " - " &amp; B757, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="758">
-      <c r="C758">
-        <f>IF(A758&lt;&gt;"", A758 &amp; " - " &amp; B758, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="759">
-      <c r="C759">
-        <f>IF(A759&lt;&gt;"", A759 &amp; " - " &amp; B759, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="760">
-      <c r="C760">
-        <f>IF(A760&lt;&gt;"", A760 &amp; " - " &amp; B760, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="761">
-      <c r="C761">
-        <f>IF(A761&lt;&gt;"", A761 &amp; " - " &amp; B761, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="762">
-      <c r="C762">
-        <f>IF(A762&lt;&gt;"", A762 &amp; " - " &amp; B762, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="763">
-      <c r="C763">
-        <f>IF(A763&lt;&gt;"", A763 &amp; " - " &amp; B763, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="764">
-      <c r="C764">
-        <f>IF(A764&lt;&gt;"", A764 &amp; " - " &amp; B764, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="765">
-      <c r="C765">
-        <f>IF(A765&lt;&gt;"", A765 &amp; " - " &amp; B765, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="766">
-      <c r="C766">
-        <f>IF(A766&lt;&gt;"", A766 &amp; " - " &amp; B766, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="767">
-      <c r="C767">
-        <f>IF(A767&lt;&gt;"", A767 &amp; " - " &amp; B767, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="768">
-      <c r="C768">
-        <f>IF(A768&lt;&gt;"", A768 &amp; " - " &amp; B768, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="769">
-      <c r="C769">
-        <f>IF(A769&lt;&gt;"", A769 &amp; " - " &amp; B769, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="770">
-      <c r="C770">
-        <f>IF(A770&lt;&gt;"", A770 &amp; " - " &amp; B770, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="771">
-      <c r="C771">
-        <f>IF(A771&lt;&gt;"", A771 &amp; " - " &amp; B771, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="772">
-      <c r="C772">
-        <f>IF(A772&lt;&gt;"", A772 &amp; " - " &amp; B772, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="773">
-      <c r="C773">
-        <f>IF(A773&lt;&gt;"", A773 &amp; " - " &amp; B773, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="774">
-      <c r="C774">
-        <f>IF(A774&lt;&gt;"", A774 &amp; " - " &amp; B774, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="775">
-      <c r="C775">
-        <f>IF(A775&lt;&gt;"", A775 &amp; " - " &amp; B775, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="776">
-      <c r="C776">
-        <f>IF(A776&lt;&gt;"", A776 &amp; " - " &amp; B776, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="777">
-      <c r="C777">
-        <f>IF(A777&lt;&gt;"", A777 &amp; " - " &amp; B777, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="778">
-      <c r="C778">
-        <f>IF(A778&lt;&gt;"", A778 &amp; " - " &amp; B778, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="779">
-      <c r="C779">
-        <f>IF(A779&lt;&gt;"", A779 &amp; " - " &amp; B779, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="780">
-      <c r="C780">
-        <f>IF(A780&lt;&gt;"", A780 &amp; " - " &amp; B780, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="781">
-      <c r="C781">
-        <f>IF(A781&lt;&gt;"", A781 &amp; " - " &amp; B781, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="782">
-      <c r="C782">
-        <f>IF(A782&lt;&gt;"", A782 &amp; " - " &amp; B782, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="783">
-      <c r="C783">
-        <f>IF(A783&lt;&gt;"", A783 &amp; " - " &amp; B783, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="784">
-      <c r="C784">
-        <f>IF(A784&lt;&gt;"", A784 &amp; " - " &amp; B784, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="785">
-      <c r="C785">
-        <f>IF(A785&lt;&gt;"", A785 &amp; " - " &amp; B785, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="786">
-      <c r="C786">
-        <f>IF(A786&lt;&gt;"", A786 &amp; " - " &amp; B786, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="787">
-      <c r="C787">
-        <f>IF(A787&lt;&gt;"", A787 &amp; " - " &amp; B787, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="788">
-      <c r="C788">
-        <f>IF(A788&lt;&gt;"", A788 &amp; " - " &amp; B788, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="789">
-      <c r="C789">
-        <f>IF(A789&lt;&gt;"", A789 &amp; " - " &amp; B789, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="790">
-      <c r="C790">
-        <f>IF(A790&lt;&gt;"", A790 &amp; " - " &amp; B790, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="791">
-      <c r="C791">
-        <f>IF(A791&lt;&gt;"", A791 &amp; " - " &amp; B791, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="792">
-      <c r="C792">
-        <f>IF(A792&lt;&gt;"", A792 &amp; " - " &amp; B792, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="793">
-      <c r="C793">
-        <f>IF(A793&lt;&gt;"", A793 &amp; " - " &amp; B793, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="794">
-      <c r="C794">
-        <f>IF(A794&lt;&gt;"", A794 &amp; " - " &amp; B794, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="795">
-      <c r="C795">
-        <f>IF(A795&lt;&gt;"", A795 &amp; " - " &amp; B795, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="796">
-      <c r="C796">
-        <f>IF(A796&lt;&gt;"", A796 &amp; " - " &amp; B796, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="797">
-      <c r="C797">
-        <f>IF(A797&lt;&gt;"", A797 &amp; " - " &amp; B797, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="798">
-      <c r="C798">
-        <f>IF(A798&lt;&gt;"", A798 &amp; " - " &amp; B798, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="799">
-      <c r="C799">
-        <f>IF(A799&lt;&gt;"", A799 &amp; " - " &amp; B799, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="800">
-      <c r="C800">
-        <f>IF(A800&lt;&gt;"", A800 &amp; " - " &amp; B800, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="801">
-      <c r="C801">
-        <f>IF(A801&lt;&gt;"", A801 &amp; " - " &amp; B801, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="802">
-      <c r="C802">
-        <f>IF(A802&lt;&gt;"", A802 &amp; " - " &amp; B802, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="803">
-      <c r="C803">
-        <f>IF(A803&lt;&gt;"", A803 &amp; " - " &amp; B803, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="804">
-      <c r="C804">
-        <f>IF(A804&lt;&gt;"", A804 &amp; " - " &amp; B804, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="805">
-      <c r="C805">
-        <f>IF(A805&lt;&gt;"", A805 &amp; " - " &amp; B805, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="806">
-      <c r="C806">
-        <f>IF(A806&lt;&gt;"", A806 &amp; " - " &amp; B806, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="807">
-      <c r="C807">
-        <f>IF(A807&lt;&gt;"", A807 &amp; " - " &amp; B807, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="808">
-      <c r="C808">
-        <f>IF(A808&lt;&gt;"", A808 &amp; " - " &amp; B808, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="809">
-      <c r="C809">
-        <f>IF(A809&lt;&gt;"", A809 &amp; " - " &amp; B809, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="810">
-      <c r="C810">
-        <f>IF(A810&lt;&gt;"", A810 &amp; " - " &amp; B810, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="811">
-      <c r="C811">
-        <f>IF(A811&lt;&gt;"", A811 &amp; " - " &amp; B811, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="812">
-      <c r="C812">
-        <f>IF(A812&lt;&gt;"", A812 &amp; " - " &amp; B812, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="813">
-      <c r="C813">
-        <f>IF(A813&lt;&gt;"", A813 &amp; " - " &amp; B813, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="814">
-      <c r="C814">
-        <f>IF(A814&lt;&gt;"", A814 &amp; " - " &amp; B814, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="815">
-      <c r="C815">
-        <f>IF(A815&lt;&gt;"", A815 &amp; " - " &amp; B815, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="816">
-      <c r="C816">
-        <f>IF(A816&lt;&gt;"", A816 &amp; " - " &amp; B816, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="817">
-      <c r="C817">
-        <f>IF(A817&lt;&gt;"", A817 &amp; " - " &amp; B817, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="818">
-      <c r="C818">
-        <f>IF(A818&lt;&gt;"", A818 &amp; " - " &amp; B818, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="819">
-      <c r="C819">
-        <f>IF(A819&lt;&gt;"", A819 &amp; " - " &amp; B819, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="820">
-      <c r="C820">
-        <f>IF(A820&lt;&gt;"", A820 &amp; " - " &amp; B820, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="821">
-      <c r="C821">
-        <f>IF(A821&lt;&gt;"", A821 &amp; " - " &amp; B821, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="822">
-      <c r="C822">
-        <f>IF(A822&lt;&gt;"", A822 &amp; " - " &amp; B822, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="823">
-      <c r="C823">
-        <f>IF(A823&lt;&gt;"", A823 &amp; " - " &amp; B823, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="824">
-      <c r="C824">
-        <f>IF(A824&lt;&gt;"", A824 &amp; " - " &amp; B824, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="825">
-      <c r="C825">
-        <f>IF(A825&lt;&gt;"", A825 &amp; " - " &amp; B825, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="826">
-      <c r="C826">
-        <f>IF(A826&lt;&gt;"", A826 &amp; " - " &amp; B826, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="827">
-      <c r="C827">
-        <f>IF(A827&lt;&gt;"", A827 &amp; " - " &amp; B827, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="828">
-      <c r="C828">
-        <f>IF(A828&lt;&gt;"", A828 &amp; " - " &amp; B828, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="829">
-      <c r="C829">
-        <f>IF(A829&lt;&gt;"", A829 &amp; " - " &amp; B829, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="830">
-      <c r="C830">
-        <f>IF(A830&lt;&gt;"", A830 &amp; " - " &amp; B830, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="831">
-      <c r="C831">
-        <f>IF(A831&lt;&gt;"", A831 &amp; " - " &amp; B831, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="832">
-      <c r="C832">
-        <f>IF(A832&lt;&gt;"", A832 &amp; " - " &amp; B832, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="833">
-      <c r="C833">
-        <f>IF(A833&lt;&gt;"", A833 &amp; " - " &amp; B833, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="834">
-      <c r="C834">
-        <f>IF(A834&lt;&gt;"", A834 &amp; " - " &amp; B834, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="835">
-      <c r="C835">
-        <f>IF(A835&lt;&gt;"", A835 &amp; " - " &amp; B835, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="836">
-      <c r="C836">
-        <f>IF(A836&lt;&gt;"", A836 &amp; " - " &amp; B836, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="837">
-      <c r="C837">
-        <f>IF(A837&lt;&gt;"", A837 &amp; " - " &amp; B837, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="838">
-      <c r="C838">
-        <f>IF(A838&lt;&gt;"", A838 &amp; " - " &amp; B838, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="839">
-      <c r="C839">
-        <f>IF(A839&lt;&gt;"", A839 &amp; " - " &amp; B839, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="840">
-      <c r="C840">
-        <f>IF(A840&lt;&gt;"", A840 &amp; " - " &amp; B840, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="841">
-      <c r="C841">
-        <f>IF(A841&lt;&gt;"", A841 &amp; " - " &amp; B841, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="842">
-      <c r="C842">
-        <f>IF(A842&lt;&gt;"", A842 &amp; " - " &amp; B842, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="843">
-      <c r="C843">
-        <f>IF(A843&lt;&gt;"", A843 &amp; " - " &amp; B843, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="844">
-      <c r="C844">
-        <f>IF(A844&lt;&gt;"", A844 &amp; " - " &amp; B844, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="845">
-      <c r="C845">
-        <f>IF(A845&lt;&gt;"", A845 &amp; " - " &amp; B845, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="846">
-      <c r="C846">
-        <f>IF(A846&lt;&gt;"", A846 &amp; " - " &amp; B846, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="847">
-      <c r="C847">
-        <f>IF(A847&lt;&gt;"", A847 &amp; " - " &amp; B847, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="848">
-      <c r="C848">
-        <f>IF(A848&lt;&gt;"", A848 &amp; " - " &amp; B848, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="849">
-      <c r="C849">
-        <f>IF(A849&lt;&gt;"", A849 &amp; " - " &amp; B849, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="850">
-      <c r="C850">
-        <f>IF(A850&lt;&gt;"", A850 &amp; " - " &amp; B850, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="851">
-      <c r="C851">
-        <f>IF(A851&lt;&gt;"", A851 &amp; " - " &amp; B851, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="852">
-      <c r="C852">
-        <f>IF(A852&lt;&gt;"", A852 &amp; " - " &amp; B852, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="853">
-      <c r="C853">
-        <f>IF(A853&lt;&gt;"", A853 &amp; " - " &amp; B853, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="854">
-      <c r="C854">
-        <f>IF(A854&lt;&gt;"", A854 &amp; " - " &amp; B854, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="855">
-      <c r="C855">
-        <f>IF(A855&lt;&gt;"", A855 &amp; " - " &amp; B855, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="856">
-      <c r="C856">
-        <f>IF(A856&lt;&gt;"", A856 &amp; " - " &amp; B856, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="857">
-      <c r="C857">
-        <f>IF(A857&lt;&gt;"", A857 &amp; " - " &amp; B857, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="858">
-      <c r="C858">
-        <f>IF(A858&lt;&gt;"", A858 &amp; " - " &amp; B858, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="859">
-      <c r="C859">
-        <f>IF(A859&lt;&gt;"", A859 &amp; " - " &amp; B859, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="860">
-      <c r="C860">
-        <f>IF(A860&lt;&gt;"", A860 &amp; " - " &amp; B860, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="861">
-      <c r="C861">
-        <f>IF(A861&lt;&gt;"", A861 &amp; " - " &amp; B861, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="862">
-      <c r="C862">
-        <f>IF(A862&lt;&gt;"", A862 &amp; " - " &amp; B862, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="863">
-      <c r="C863">
-        <f>IF(A863&lt;&gt;"", A863 &amp; " - " &amp; B863, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="864">
-      <c r="C864">
-        <f>IF(A864&lt;&gt;"", A864 &amp; " - " &amp; B864, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="865">
-      <c r="C865">
-        <f>IF(A865&lt;&gt;"", A865 &amp; " - " &amp; B865, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="866">
-      <c r="C866">
-        <f>IF(A866&lt;&gt;"", A866 &amp; " - " &amp; B866, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="867">
-      <c r="C867">
-        <f>IF(A867&lt;&gt;"", A867 &amp; " - " &amp; B867, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="868">
-      <c r="C868">
-        <f>IF(A868&lt;&gt;"", A868 &amp; " - " &amp; B868, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="869">
-      <c r="C869">
-        <f>IF(A869&lt;&gt;"", A869 &amp; " - " &amp; B869, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="870">
-      <c r="C870">
-        <f>IF(A870&lt;&gt;"", A870 &amp; " - " &amp; B870, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="871">
-      <c r="C871">
-        <f>IF(A871&lt;&gt;"", A871 &amp; " - " &amp; B871, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="872">
-      <c r="C872">
-        <f>IF(A872&lt;&gt;"", A872 &amp; " - " &amp; B872, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="873">
-      <c r="C873">
-        <f>IF(A873&lt;&gt;"", A873 &amp; " - " &amp; B873, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="874">
-      <c r="C874">
-        <f>IF(A874&lt;&gt;"", A874 &amp; " - " &amp; B874, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="875">
-      <c r="C875">
-        <f>IF(A875&lt;&gt;"", A875 &amp; " - " &amp; B875, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="876">
-      <c r="C876">
-        <f>IF(A876&lt;&gt;"", A876 &amp; " - " &amp; B876, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="877">
-      <c r="C877">
-        <f>IF(A877&lt;&gt;"", A877 &amp; " - " &amp; B877, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="878">
-      <c r="C878">
-        <f>IF(A878&lt;&gt;"", A878 &amp; " - " &amp; B878, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="879">
-      <c r="C879">
-        <f>IF(A879&lt;&gt;"", A879 &amp; " - " &amp; B879, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="880">
-      <c r="C880">
-        <f>IF(A880&lt;&gt;"", A880 &amp; " - " &amp; B880, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="881">
-      <c r="C881">
-        <f>IF(A881&lt;&gt;"", A881 &amp; " - " &amp; B881, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="882">
-      <c r="C882">
-        <f>IF(A882&lt;&gt;"", A882 &amp; " - " &amp; B882, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="883">
-      <c r="C883">
-        <f>IF(A883&lt;&gt;"", A883 &amp; " - " &amp; B883, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="884">
-      <c r="C884">
-        <f>IF(A884&lt;&gt;"", A884 &amp; " - " &amp; B884, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="885">
-      <c r="C885">
-        <f>IF(A885&lt;&gt;"", A885 &amp; " - " &amp; B885, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="886">
-      <c r="C886">
-        <f>IF(A886&lt;&gt;"", A886 &amp; " - " &amp; B886, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="887">
-      <c r="C887">
-        <f>IF(A887&lt;&gt;"", A887 &amp; " - " &amp; B887, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="888">
-      <c r="C888">
-        <f>IF(A888&lt;&gt;"", A888 &amp; " - " &amp; B888, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="889">
-      <c r="C889">
-        <f>IF(A889&lt;&gt;"", A889 &amp; " - " &amp; B889, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="890">
-      <c r="C890">
-        <f>IF(A890&lt;&gt;"", A890 &amp; " - " &amp; B890, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="891">
-      <c r="C891">
-        <f>IF(A891&lt;&gt;"", A891 &amp; " - " &amp; B891, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="892">
-      <c r="C892">
-        <f>IF(A892&lt;&gt;"", A892 &amp; " - " &amp; B892, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="893">
-      <c r="C893">
-        <f>IF(A893&lt;&gt;"", A893 &amp; " - " &amp; B893, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="894">
-      <c r="C894">
-        <f>IF(A894&lt;&gt;"", A894 &amp; " - " &amp; B894, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="895">
-      <c r="C895">
-        <f>IF(A895&lt;&gt;"", A895 &amp; " - " &amp; B895, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="896">
-      <c r="C896">
-        <f>IF(A896&lt;&gt;"", A896 &amp; " - " &amp; B896, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="897">
-      <c r="C897">
-        <f>IF(A897&lt;&gt;"", A897 &amp; " - " &amp; B897, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="898">
-      <c r="C898">
-        <f>IF(A898&lt;&gt;"", A898 &amp; " - " &amp; B898, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="899">
-      <c r="C899">
-        <f>IF(A899&lt;&gt;"", A899 &amp; " - " &amp; B899, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="900">
-      <c r="C900">
-        <f>IF(A900&lt;&gt;"", A900 &amp; " - " &amp; B900, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="901">
-      <c r="C901">
-        <f>IF(A901&lt;&gt;"", A901 &amp; " - " &amp; B901, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="902">
-      <c r="C902">
-        <f>IF(A902&lt;&gt;"", A902 &amp; " - " &amp; B902, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="903">
-      <c r="C903">
-        <f>IF(A903&lt;&gt;"", A903 &amp; " - " &amp; B903, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="904">
-      <c r="C904">
-        <f>IF(A904&lt;&gt;"", A904 &amp; " - " &amp; B904, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="905">
-      <c r="C905">
-        <f>IF(A905&lt;&gt;"", A905 &amp; " - " &amp; B905, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="906">
-      <c r="C906">
-        <f>IF(A906&lt;&gt;"", A906 &amp; " - " &amp; B906, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="907">
-      <c r="C907">
-        <f>IF(A907&lt;&gt;"", A907 &amp; " - " &amp; B907, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="908">
-      <c r="C908">
-        <f>IF(A908&lt;&gt;"", A908 &amp; " - " &amp; B908, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="909">
-      <c r="C909">
-        <f>IF(A909&lt;&gt;"", A909 &amp; " - " &amp; B909, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="910">
-      <c r="C910">
-        <f>IF(A910&lt;&gt;"", A910 &amp; " - " &amp; B910, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="911">
-      <c r="C911">
-        <f>IF(A911&lt;&gt;"", A911 &amp; " - " &amp; B911, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="912">
-      <c r="C912">
-        <f>IF(A912&lt;&gt;"", A912 &amp; " - " &amp; B912, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="913">
-      <c r="C913">
-        <f>IF(A913&lt;&gt;"", A913 &amp; " - " &amp; B913, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="914">
-      <c r="C914">
-        <f>IF(A914&lt;&gt;"", A914 &amp; " - " &amp; B914, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="915">
-      <c r="C915">
-        <f>IF(A915&lt;&gt;"", A915 &amp; " - " &amp; B915, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="916">
-      <c r="C916">
-        <f>IF(A916&lt;&gt;"", A916 &amp; " - " &amp; B916, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="917">
-      <c r="C917">
-        <f>IF(A917&lt;&gt;"", A917 &amp; " - " &amp; B917, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="918">
-      <c r="C918">
-        <f>IF(A918&lt;&gt;"", A918 &amp; " - " &amp; B918, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="919">
-      <c r="C919">
-        <f>IF(A919&lt;&gt;"", A919 &amp; " - " &amp; B919, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="920">
-      <c r="C920">
-        <f>IF(A920&lt;&gt;"", A920 &amp; " - " &amp; B920, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="921">
-      <c r="C921">
-        <f>IF(A921&lt;&gt;"", A921 &amp; " - " &amp; B921, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="922">
-      <c r="C922">
-        <f>IF(A922&lt;&gt;"", A922 &amp; " - " &amp; B922, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="923">
-      <c r="C923">
-        <f>IF(A923&lt;&gt;"", A923 &amp; " - " &amp; B923, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="924">
-      <c r="C924">
-        <f>IF(A924&lt;&gt;"", A924 &amp; " - " &amp; B924, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="925">
-      <c r="C925">
-        <f>IF(A925&lt;&gt;"", A925 &amp; " - " &amp; B925, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="926">
-      <c r="C926">
-        <f>IF(A926&lt;&gt;"", A926 &amp; " - " &amp; B926, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="927">
-      <c r="C927">
-        <f>IF(A927&lt;&gt;"", A927 &amp; " - " &amp; B927, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="928">
-      <c r="C928">
-        <f>IF(A928&lt;&gt;"", A928 &amp; " - " &amp; B928, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="929">
-      <c r="C929">
-        <f>IF(A929&lt;&gt;"", A929 &amp; " - " &amp; B929, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="930">
-      <c r="C930">
-        <f>IF(A930&lt;&gt;"", A930 &amp; " - " &amp; B930, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="931">
-      <c r="C931">
-        <f>IF(A931&lt;&gt;"", A931 &amp; " - " &amp; B931, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="932">
-      <c r="C932">
-        <f>IF(A932&lt;&gt;"", A932 &amp; " - " &amp; B932, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="933">
-      <c r="C933">
-        <f>IF(A933&lt;&gt;"", A933 &amp; " - " &amp; B933, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="934">
-      <c r="C934">
-        <f>IF(A934&lt;&gt;"", A934 &amp; " - " &amp; B934, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="935">
-      <c r="C935">
-        <f>IF(A935&lt;&gt;"", A935 &amp; " - " &amp; B935, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="936">
-      <c r="C936">
-        <f>IF(A936&lt;&gt;"", A936 &amp; " - " &amp; B936, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="937">
-      <c r="C937">
-        <f>IF(A937&lt;&gt;"", A937 &amp; " - " &amp; B937, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="938">
-      <c r="C938">
-        <f>IF(A938&lt;&gt;"", A938 &amp; " - " &amp; B938, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="939">
-      <c r="C939">
-        <f>IF(A939&lt;&gt;"", A939 &amp; " - " &amp; B939, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="940">
-      <c r="C940">
-        <f>IF(A940&lt;&gt;"", A940 &amp; " - " &amp; B940, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="941">
-      <c r="C941">
-        <f>IF(A941&lt;&gt;"", A941 &amp; " - " &amp; B941, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="942">
-      <c r="C942">
-        <f>IF(A942&lt;&gt;"", A942 &amp; " - " &amp; B942, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="943">
-      <c r="C943">
-        <f>IF(A943&lt;&gt;"", A943 &amp; " - " &amp; B943, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="944">
-      <c r="C944">
-        <f>IF(A944&lt;&gt;"", A944 &amp; " - " &amp; B944, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="945">
-      <c r="C945">
-        <f>IF(A945&lt;&gt;"", A945 &amp; " - " &amp; B945, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="946">
-      <c r="C946">
-        <f>IF(A946&lt;&gt;"", A946 &amp; " - " &amp; B946, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="947">
-      <c r="C947">
-        <f>IF(A947&lt;&gt;"", A947 &amp; " - " &amp; B947, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="948">
-      <c r="C948">
-        <f>IF(A948&lt;&gt;"", A948 &amp; " - " &amp; B948, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="949">
-      <c r="C949">
-        <f>IF(A949&lt;&gt;"", A949 &amp; " - " &amp; B949, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="950">
-      <c r="C950">
-        <f>IF(A950&lt;&gt;"", A950 &amp; " - " &amp; B950, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="951">
-      <c r="C951">
-        <f>IF(A951&lt;&gt;"", A951 &amp; " - " &amp; B951, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="952">
-      <c r="C952">
-        <f>IF(A952&lt;&gt;"", A952 &amp; " - " &amp; B952, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="953">
-      <c r="C953">
-        <f>IF(A953&lt;&gt;"", A953 &amp; " - " &amp; B953, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="954">
-      <c r="C954">
-        <f>IF(A954&lt;&gt;"", A954 &amp; " - " &amp; B954, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="955">
-      <c r="C955">
-        <f>IF(A955&lt;&gt;"", A955 &amp; " - " &amp; B955, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="956">
-      <c r="C956">
-        <f>IF(A956&lt;&gt;"", A956 &amp; " - " &amp; B956, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="957">
-      <c r="C957">
-        <f>IF(A957&lt;&gt;"", A957 &amp; " - " &amp; B957, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="958">
-      <c r="C958">
-        <f>IF(A958&lt;&gt;"", A958 &amp; " - " &amp; B958, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="959">
-      <c r="C959">
-        <f>IF(A959&lt;&gt;"", A959 &amp; " - " &amp; B959, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="960">
-      <c r="C960">
-        <f>IF(A960&lt;&gt;"", A960 &amp; " - " &amp; B960, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="961">
-      <c r="C961">
-        <f>IF(A961&lt;&gt;"", A961 &amp; " - " &amp; B961, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="962">
-      <c r="C962">
-        <f>IF(A962&lt;&gt;"", A962 &amp; " - " &amp; B962, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="963">
-      <c r="C963">
-        <f>IF(A963&lt;&gt;"", A963 &amp; " - " &amp; B963, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="964">
-      <c r="C964">
-        <f>IF(A964&lt;&gt;"", A964 &amp; " - " &amp; B964, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="965">
-      <c r="C965">
-        <f>IF(A965&lt;&gt;"", A965 &amp; " - " &amp; B965, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="966">
-      <c r="C966">
-        <f>IF(A966&lt;&gt;"", A966 &amp; " - " &amp; B966, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="967">
-      <c r="C967">
-        <f>IF(A967&lt;&gt;"", A967 &amp; " - " &amp; B967, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="968">
-      <c r="C968">
-        <f>IF(A968&lt;&gt;"", A968 &amp; " - " &amp; B968, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="969">
-      <c r="C969">
-        <f>IF(A969&lt;&gt;"", A969 &amp; " - " &amp; B969, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="970">
-      <c r="C970">
-        <f>IF(A970&lt;&gt;"", A970 &amp; " - " &amp; B970, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="971">
-      <c r="C971">
-        <f>IF(A971&lt;&gt;"", A971 &amp; " - " &amp; B971, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="972">
-      <c r="C972">
-        <f>IF(A972&lt;&gt;"", A972 &amp; " - " &amp; B972, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="973">
-      <c r="C973">
-        <f>IF(A973&lt;&gt;"", A973 &amp; " - " &amp; B973, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="974">
-      <c r="C974">
-        <f>IF(A974&lt;&gt;"", A974 &amp; " - " &amp; B974, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="975">
-      <c r="C975">
-        <f>IF(A975&lt;&gt;"", A975 &amp; " - " &amp; B975, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="976">
-      <c r="C976">
-        <f>IF(A976&lt;&gt;"", A976 &amp; " - " &amp; B976, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="977">
-      <c r="C977">
-        <f>IF(A977&lt;&gt;"", A977 &amp; " - " &amp; B977, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="978">
-      <c r="C978">
-        <f>IF(A978&lt;&gt;"", A978 &amp; " - " &amp; B978, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="979">
-      <c r="C979">
-        <f>IF(A979&lt;&gt;"", A979 &amp; " - " &amp; B979, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="980">
-      <c r="C980">
-        <f>IF(A980&lt;&gt;"", A980 &amp; " - " &amp; B980, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="981">
-      <c r="C981">
-        <f>IF(A981&lt;&gt;"", A981 &amp; " - " &amp; B981, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="982">
-      <c r="C982">
-        <f>IF(A982&lt;&gt;"", A982 &amp; " - " &amp; B982, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="983">
-      <c r="C983">
-        <f>IF(A983&lt;&gt;"", A983 &amp; " - " &amp; B983, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="984">
-      <c r="C984">
-        <f>IF(A984&lt;&gt;"", A984 &amp; " - " &amp; B984, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="985">
-      <c r="C985">
-        <f>IF(A985&lt;&gt;"", A985 &amp; " - " &amp; B985, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="986">
-      <c r="C986">
-        <f>IF(A986&lt;&gt;"", A986 &amp; " - " &amp; B986, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="987">
-      <c r="C987">
-        <f>IF(A987&lt;&gt;"", A987 &amp; " - " &amp; B987, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="988">
-      <c r="C988">
-        <f>IF(A988&lt;&gt;"", A988 &amp; " - " &amp; B988, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="989">
-      <c r="C989">
-        <f>IF(A989&lt;&gt;"", A989 &amp; " - " &amp; B989, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="990">
-      <c r="C990">
-        <f>IF(A990&lt;&gt;"", A990 &amp; " - " &amp; B990, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="991">
-      <c r="C991">
-        <f>IF(A991&lt;&gt;"", A991 &amp; " - " &amp; B991, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="992">
-      <c r="C992">
-        <f>IF(A992&lt;&gt;"", A992 &amp; " - " &amp; B992, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="993">
-      <c r="C993">
-        <f>IF(A993&lt;&gt;"", A993 &amp; " - " &amp; B993, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="994">
-      <c r="C994">
-        <f>IF(A994&lt;&gt;"", A994 &amp; " - " &amp; B994, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="995">
-      <c r="C995">
-        <f>IF(A995&lt;&gt;"", A995 &amp; " - " &amp; B995, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="996">
-      <c r="C996">
-        <f>IF(A996&lt;&gt;"", A996 &amp; " - " &amp; B996, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="997">
-      <c r="C997">
-        <f>IF(A997&lt;&gt;"", A997 &amp; " - " &amp; B997, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="998">
-      <c r="C998">
-        <f>IF(A998&lt;&gt;"", A998 &amp; " - " &amp; B998, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="999">
-      <c r="C999">
-        <f>IF(A999&lt;&gt;"", A999 &amp; " - " &amp; B999, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="1000">
-      <c r="C1000">
-        <f>IF(A1000&lt;&gt;"", A1000 &amp; " - " &amp; B1000, "")</f>
-        <v/>
+          <t>Konto</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7118,7 +522,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Lieferant (Name oder MwSt-Nr)</t>
+          <t>Stichwort in Beschreibung</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -7128,51 +532,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiges Konto" error="Das eingegebene Konto existiert nicht im Kontenplan!" promptTitle="Konto auswählen" prompt="Bitte ein Konto aus der Dropdown-Liste wählen" type="list">
-      <formula1>'Kontenplan'!$C$2:$C$1000</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Stichwort in Beschreibung</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Konto</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Ungültiges Konto" error="Das eingegebene Konto existiert nicht im Kontenplan!" promptTitle="Konto auswählen" prompt="Bitte ein Konto aus der Dropdown-Liste wählen" type="list">
-      <formula1>'Kontenplan'!$C$2:$C$1000</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
